--- a/MPL-Standings.xlsx
+++ b/MPL-Standings.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Archieve\Code\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB62C95-7BD7-4F7D-AC24-3E40BDD6984E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B56D98-A98D-40FB-A03B-F2AF19DA5732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{C5244675-7051-49A0-9076-7228300D05A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{C5244675-7051-49A0-9076-7228300D05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="MPL ID" sheetId="1" r:id="rId1"/>
     <sheet name="MPL PH" sheetId="4" r:id="rId2"/>
-    <sheet name="MPL MY" sheetId="5" r:id="rId3"/>
+    <sheet name="MPL MY" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'MPL ID'!$A$1:$T$58</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="69">
   <si>
     <t>Week 1</t>
   </si>
@@ -219,6 +219,30 @@
   </si>
   <si>
     <t>TEAM</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>BTR MY</t>
+  </si>
+  <si>
+    <t>RRQ T</t>
+  </si>
+  <si>
+    <t>SRG</t>
+  </si>
+  <si>
+    <t>T. FLASH</t>
+  </si>
+  <si>
+    <t>T. REY</t>
+  </si>
+  <si>
+    <t>T. VAMOS</t>
+  </si>
+  <si>
+    <t>IG</t>
   </si>
 </sst>
 </file>
@@ -929,140 +953,8 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1094,6 +986,138 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,8 +1141,14 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -1127,8 +1157,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1171,6 +1199,12 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1195,6 +1229,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1272,6 +1313,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1279,6 +1327,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1342,6 +1397,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1433,6 +1495,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1524,6 +1593,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1531,6 +1607,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1594,6 +1677,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1685,6 +1775,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1776,6 +1873,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1783,6 +1887,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1846,6 +1957,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1937,125 +2055,16 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2095,13 +2104,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -2112,6 +2114,38 @@
           <color rgb="FF000000"/>
         </top>
         <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
       </border>
@@ -2263,9 +2297,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7FF5B943-0912-466E-9E82-8A7F0750EDE2}" name="Table25" displayName="Table25" ref="B2:B11" totalsRowShown="0" headerRowDxfId="129" dataDxfId="125" headerRowBorderDxfId="127" tableBorderDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7FF5B943-0912-466E-9E82-8A7F0750EDE2}" name="Table25" displayName="Table25" ref="B2:B11" totalsRowShown="0" headerRowDxfId="129" dataDxfId="127" headerRowBorderDxfId="128" tableBorderDxfId="126">
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{B4480FFE-5004-446E-8621-4A5EF58DC078}" name="TEAM" dataDxfId="126">
+    <tableColumn id="1" xr3:uid="{B4480FFE-5004-446E-8621-4A5EF58DC078}" name="TEAM" dataDxfId="125">
       <calculatedColumnFormula>INDEX($BF$1:$BF$8,MATCH(ROW()-1,$BJ$1:$BJ$8,0))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2274,10 +2308,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{999E06C1-4FE6-492E-BA39-E5291E2A3446}" name="Table26" displayName="Table26" ref="B2:B11" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2DB16CEA-9339-4432-9859-9F9E67763548}" name="Table252" displayName="Table252" ref="B2:B11" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3" headerRowBorderDxfId="1" tableBorderDxfId="2">
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{696BDA9A-3521-40DA-8C9B-15EBA34616CD}" name="TIM" dataDxfId="0">
-      <calculatedColumnFormula>INDEX($BF$1:$BF$9,MATCH(ROW()-2,$BJ$1:$BJ$9,0))</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{0E3A6131-3F74-4BAB-B47B-6E76D2FEA7EA}" name="TEAM" dataDxfId="0">
+      <calculatedColumnFormula>INDEX($BF$1:$BF$8,MATCH(ROW()-1,$BJ$1:$BJ$8,0))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2610,21 +2644,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="70"/>
-      <c r="I1" s="71" t="s">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="85"/>
+      <c r="I1" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
       <c r="M1" s="7"/>
       <c r="N1" s="14"/>
       <c r="O1" s="7"/>
@@ -2674,18 +2708,18 @@
       <c r="G2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="97"/>
       <c r="BF2" s="25" t="s">
         <v>21</v>
       </c>
@@ -2735,16 +2769,16 @@
         <f t="shared" ref="G3:G11" si="5">E3-F3</f>
         <v>12</v>
       </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="61"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="97"/>
       <c r="BF3" s="25" t="s">
         <v>36</v>
       </c>
@@ -2794,16 +2828,16 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="61"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="97"/>
       <c r="BF4" s="25" t="s">
         <v>22</v>
       </c>
@@ -2853,16 +2887,16 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="I5" s="59"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="61"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="97"/>
       <c r="BF5" s="25" t="s">
         <v>38</v>
       </c>
@@ -2912,16 +2946,16 @@
         <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="61"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
       <c r="BF6" s="25" t="s">
         <v>23</v>
       </c>
@@ -2971,16 +3005,16 @@
         <f t="shared" si="5"/>
         <v>-2</v>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="61"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="97"/>
       <c r="BF7" s="25" t="s">
         <v>24</v>
       </c>
@@ -3030,16 +3064,16 @@
         <f t="shared" si="5"/>
         <v>-2</v>
       </c>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="61"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="97"/>
       <c r="BF8" s="25" t="s">
         <v>37</v>
       </c>
@@ -3089,16 +3123,16 @@
         <f t="shared" si="5"/>
         <v>-5</v>
       </c>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="61"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="97"/>
       <c r="BF9" s="25" t="s">
         <v>25</v>
       </c>
@@ -3148,18 +3182,18 @@
         <f t="shared" si="5"/>
         <v>-10</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="64"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="100"/>
     </row>
     <row r="11" spans="1:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
@@ -3220,27 +3254,27 @@
       </c>
     </row>
     <row r="13" spans="1:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="67"/>
-      <c r="H13" s="65" t="s">
+      <c r="B13" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="88"/>
+      <c r="H13" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="66"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="67"/>
-      <c r="N13" s="65" t="s">
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="88"/>
+      <c r="N13" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="67"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
       <c r="BF13" s="25" t="s">
         <v>20</v>
       </c>
@@ -3957,27 +3991,27 @@
       </c>
     </row>
     <row r="24" spans="2:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="65" t="s">
+      <c r="B24" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="67"/>
-      <c r="H24" s="65" t="s">
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="88"/>
+      <c r="H24" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="67"/>
-      <c r="N24" s="65" t="s">
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="88"/>
+      <c r="N24" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="67"/>
+      <c r="O24" s="87"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
     </row>
     <row r="25" spans="2:67" x14ac:dyDescent="0.25">
       <c r="B25" s="22" t="s">
@@ -4339,27 +4373,27 @@
       </c>
     </row>
     <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67"/>
-      <c r="H35" s="65" t="s">
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="88"/>
+      <c r="H35" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="67"/>
-      <c r="N35" s="65" t="s">
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="88"/>
+      <c r="N35" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="67"/>
+      <c r="O35" s="87"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="87"/>
+      <c r="R35" s="88"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
@@ -4630,26 +4664,26 @@
     </row>
     <row r="45" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="58"/>
-      <c r="H46" s="85" t="s">
+      <c r="C46" s="93"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="94"/>
+      <c r="H46" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="I46" s="86"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="86"/>
-      <c r="M46" s="86"/>
-      <c r="N46" s="86"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="87"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="69"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="70"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
@@ -4670,15 +4704,15 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="3"/>
-      <c r="H48" s="92" t="s">
+      <c r="H48" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="I48" s="93"/>
-      <c r="J48" s="95" t="s">
+      <c r="I48" s="80"/>
+      <c r="J48" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="K48" s="95"/>
-      <c r="L48" s="95"/>
+      <c r="K48" s="82"/>
+      <c r="L48" s="82"/>
       <c r="R48" s="10"/>
     </row>
     <row r="49" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4694,17 +4728,17 @@
         <v>NAVI</v>
       </c>
       <c r="I49" s="37"/>
-      <c r="J49" s="81" t="str">
+      <c r="J49" s="71" t="str">
         <f>B4</f>
         <v>AE</v>
       </c>
-      <c r="K49" s="82"/>
+      <c r="K49" s="72"/>
       <c r="L49" s="37"/>
-      <c r="M49" s="94" t="s">
+      <c r="M49" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="N49" s="94"/>
-      <c r="O49" s="94"/>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
       <c r="R49" s="10"/>
     </row>
     <row r="50" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4720,23 +4754,23 @@
         <v>ONIC</v>
       </c>
       <c r="I50" s="38"/>
-      <c r="J50" s="81" t="str">
+      <c r="J50" s="71" t="str">
         <f>IF(I49&gt;I50, H49, H50)</f>
         <v>ONIC</v>
       </c>
-      <c r="K50" s="82"/>
+      <c r="K50" s="72"/>
       <c r="L50" s="38"/>
-      <c r="M50" s="79" t="str">
+      <c r="M50" s="105" t="str">
         <f>IF((L49&gt;L50),J49,J50)</f>
         <v>ONIC</v>
       </c>
-      <c r="N50" s="80"/>
+      <c r="N50" s="106"/>
       <c r="O50" s="37"/>
-      <c r="P50" s="90" t="s">
+      <c r="P50" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="Q50" s="90"/>
-      <c r="R50" s="91"/>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="78"/>
     </row>
     <row r="51" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
@@ -4751,23 +4785,23 @@
         <v>EVOS</v>
       </c>
       <c r="I51" s="37"/>
-      <c r="J51" s="81" t="str">
+      <c r="J51" s="71" t="str">
         <f>B3</f>
         <v>TLID</v>
       </c>
-      <c r="K51" s="82"/>
+      <c r="K51" s="72"/>
       <c r="L51" s="37"/>
-      <c r="M51" s="79" t="str">
+      <c r="M51" s="105" t="str">
         <f>IF((L51&gt;L52),J51,J52)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="N51" s="80"/>
+      <c r="N51" s="106"/>
       <c r="O51" s="38"/>
-      <c r="P51" s="88" t="str">
+      <c r="P51" s="73" t="str">
         <f>IF((O50&gt;O51),M50,M51)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="Q51" s="89"/>
+      <c r="Q51" s="74"/>
       <c r="R51" s="44"/>
       <c r="S51" s="9"/>
     </row>
@@ -4784,23 +4818,23 @@
         <v>BTR by VIT</v>
       </c>
       <c r="I52" s="38"/>
-      <c r="J52" s="81" t="str">
+      <c r="J52" s="71" t="str">
         <f>IF(I51&gt;I52, H51, H52)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="K52" s="82"/>
+      <c r="K52" s="72"/>
       <c r="L52" s="38"/>
-      <c r="M52" s="83" t="str">
+      <c r="M52" s="66" t="str">
         <f>IF((O50&lt;O51),M50,M51)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="N52" s="84"/>
+      <c r="N52" s="67"/>
       <c r="O52" s="37"/>
-      <c r="P52" s="88" t="str">
+      <c r="P52" s="73" t="str">
         <f>IF((O52&gt;O53),M52,M53)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="Q52" s="89"/>
+      <c r="Q52" s="74"/>
       <c r="R52" s="45"/>
       <c r="S52" s="9"/>
     </row>
@@ -4812,21 +4846,21 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="3"/>
-      <c r="H53" s="92" t="s">
+      <c r="H53" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="93"/>
-      <c r="J53" s="73" t="str">
+      <c r="I53" s="80"/>
+      <c r="J53" s="75" t="str">
         <f>IF((L49&lt;L50),J49,J50)</f>
         <v>ONIC</v>
       </c>
-      <c r="K53" s="74"/>
+      <c r="K53" s="76"/>
       <c r="L53" s="37"/>
-      <c r="M53" s="83" t="str">
+      <c r="M53" s="66" t="str">
         <f>IF((L53&gt;L54),J53,J54)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="N53" s="84"/>
+      <c r="N53" s="67"/>
       <c r="O53" s="38"/>
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
@@ -4841,17 +4875,17 @@
       <c r="E54" s="1"/>
       <c r="F54" s="3"/>
       <c r="H54" s="9"/>
-      <c r="J54" s="73" t="str">
+      <c r="J54" s="75" t="str">
         <f>IF((L51&lt;L52),J51,J52)</f>
         <v>BTR by VIT</v>
       </c>
-      <c r="K54" s="74"/>
+      <c r="K54" s="76"/>
       <c r="L54" s="38"/>
-      <c r="M54" s="76" t="s">
+      <c r="M54" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="N54" s="77"/>
-      <c r="O54" s="78"/>
+      <c r="N54" s="103"/>
+      <c r="O54" s="104"/>
       <c r="R54" s="10"/>
     </row>
     <row r="55" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4863,11 +4897,11 @@
       <c r="E55" s="5"/>
       <c r="F55" s="6"/>
       <c r="H55" s="9"/>
-      <c r="J55" s="75" t="s">
+      <c r="J55" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="75"/>
-      <c r="L55" s="75"/>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
       <c r="R55" s="10"/>
     </row>
     <row r="56" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4885,36 +4919,16 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.25">
       <c r="H59" s="43"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="55"/>
+      <c r="J59" s="91"/>
+      <c r="K59" s="91"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.25">
       <c r="H61" s="43"/>
-      <c r="J61" s="55"/>
-      <c r="K61" s="55"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="H46:R46"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="P50:R50"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="H24:L24"/>
-    <mergeCell ref="H35:L35"/>
-    <mergeCell ref="I1:L1"/>
     <mergeCell ref="J59:K59"/>
     <mergeCell ref="J61:K61"/>
     <mergeCell ref="B46:F46"/>
@@ -4931,14 +4945,34 @@
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="J50:K50"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="H24:L24"/>
+    <mergeCell ref="H35:L35"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="H46:R46"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="P50:R50"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="J48:L48"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C14:C22">
-    <cfRule type="expression" dxfId="124" priority="39">
+    <cfRule type="expression" dxfId="124" priority="40">
+      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&gt;$E14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="39">
       <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&lt;$E14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="40">
-      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&gt;$E14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:C33">
@@ -4998,43 +5032,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I22">
-    <cfRule type="expression" dxfId="108" priority="31">
+    <cfRule type="expression" dxfId="108" priority="32">
+      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="31">
       <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="107" priority="32">
-      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:I33">
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
+      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="28">
-      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36:I44">
-    <cfRule type="expression" dxfId="104" priority="23">
+    <cfRule type="expression" dxfId="104" priority="24">
+      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="23">
       <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&lt;$K36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
-      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14:L22">
-    <cfRule type="expression" dxfId="102" priority="29">
+    <cfRule type="expression" dxfId="102" priority="30">
+      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="29">
       <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="30">
-      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L25:L33">
-    <cfRule type="expression" dxfId="100" priority="25">
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
       <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="26">
-      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36:L44">
@@ -5046,51 +5080,51 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O14:O22">
-    <cfRule type="expression" dxfId="96" priority="11">
+    <cfRule type="expression" dxfId="96" priority="12">
+      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="11">
       <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="12">
-      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O25:O33">
-    <cfRule type="expression" dxfId="94" priority="7">
+    <cfRule type="expression" dxfId="94" priority="8">
+      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="7">
       <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="8">
-      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O36:O44">
-    <cfRule type="expression" dxfId="92" priority="3">
+    <cfRule type="expression" dxfId="92" priority="4">
+      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="3">
       <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="4">
-      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R14:R22">
-    <cfRule type="expression" dxfId="90" priority="9">
+    <cfRule type="expression" dxfId="90" priority="10">
+      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="9">
       <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="10">
-      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R25:R33">
-    <cfRule type="expression" dxfId="88" priority="5">
+    <cfRule type="expression" dxfId="88" priority="6">
+      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="5">
       <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="6">
-      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36:R44">
-    <cfRule type="expression" dxfId="86" priority="1">
+    <cfRule type="expression" dxfId="86" priority="2">
+      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="1">
       <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="2">
-      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -5149,21 +5183,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="70"/>
-      <c r="I1" s="71" t="s">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="85"/>
+      <c r="I1" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
       <c r="M1" s="7"/>
       <c r="N1" s="14"/>
       <c r="O1" s="7"/>
@@ -5182,14 +5216,14 @@
         <v>-6</v>
       </c>
       <c r="BI1" s="25">
-        <f>IF(COUNTIFS($BG$1:$BG$8,BG1,$BH$1:$BH$8,BH1)&lt;=1,0,SUMPRODUCT(INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),0)*TRANSPOSE(($BG$1:$BG$8=BG1)*($BH$1:$BH$8=BH1))))</f>
+        <f>IF(AND($BG$1=BG1,$BH$1=BH1,$BF$1&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$1,$BG$12:$BN$12,0)),0)+IF(AND($BG$2=BG1,$BH$2=BH1,$BF$2&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$2,$BG$12:$BN$12,0)),0)+IF(AND($BG$3=BG1,$BH$3=BH1,$BF$3&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$3,$BG$12:$BN$12,0)),0)+IF(AND($BG$4=BG1,$BH$4=BH1,$BF$4&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$4,$BG$12:$BN$12,0)),0)+IF(AND($BG$5=BG1,$BH$5=BH1,$BF$5&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$5,$BG$12:$BN$12,0)),0)+IF(AND($BG$6=BG1,$BH$6=BH1,$BF$6&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$6,$BG$12:$BN$12,0)),0)+IF(AND($BG$7=BG1,$BH$7=BH1,$BF$7&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$7,$BG$12:$BN$12,0)),0)+IF(AND($BG$8=BG1,$BH$8=BH1,$BF$8&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$8,$BG$12:$BN$12,0)),0)</f>
         <v>0</v>
       </c>
       <c r="BJ1" s="25">
-        <f>IF(COUNTIFS($BG$1:$BG$8,BG1,$BH$1:$BH$8,BH1)&lt;=1,0,SUMPRODUCT(INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),0)*TRANSPOSE(($BG$1:$BG$8=BG1)*($BH$1:$BH$8=BH1))))</f>
-        <v>0</v>
-      </c>
-      <c r="BK1" s="100">
+        <f>IF(AND($BG$1=BG1,$BH$1=BH1,$BF$1&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$1,$BG$24:$BN$24,0)),0)+IF(AND($BG$2=BG1,$BH$2=BH1,$BF$2&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$2,$BG$24:$BN$24,0)),0)+IF(AND($BG$3=BG1,$BH$3=BH1,$BF$3&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$3,$BG$24:$BN$24,0)),0)+IF(AND($BG$4=BG1,$BH$4=BH1,$BF$4&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$4,$BG$24:$BN$24,0)),0)+IF(AND($BG$5=BG1,$BH$5=BH1,$BF$5&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$5,$BG$24:$BN$24,0)),0)+IF(AND($BG$6=BG1,$BH$6=BH1,$BF$6&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$6,$BG$24:$BN$24,0)),0)+IF(AND($BG$7=BG1,$BH$7=BH1,$BF$7&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$7,$BG$24:$BN$24,0)),0)+IF(AND($BG$8=BG1,$BH$8=BH1,$BF$8&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$8,$BG$24:$BN$24,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK1" s="56">
         <f>1+SUMPRODUCT(--($BG$1:$BG$8&gt;BG1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8&gt;BH1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8=BH1),--($BI$1:$BI$8&gt;BI1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8=BH1),--($BI$1:$BI$8=BI1),--($BF$1:$BF$8&lt;BF1))</f>
         <v>7</v>
       </c>
@@ -5217,18 +5251,18 @@
       <c r="G2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="97"/>
       <c r="BF2" s="25" t="s">
         <v>58</v>
       </c>
@@ -5241,14 +5275,14 @@
         <v>4</v>
       </c>
       <c r="BI2" s="25">
-        <f t="shared" ref="BI2:BI8" si="2">IF(COUNTIFS($BG$1:$BG$8,BG2,$BH$1:$BH$8,BH2)&lt;=1,0,SUMPRODUCT(INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),0)*TRANSPOSE(($BG$1:$BG$8=BG2)*($BH$1:$BH$8=BH2))))</f>
+        <f t="shared" ref="BI2:BI8" si="2">IF(AND($BG$1=BG2,$BH$1=BH2,$BF$1&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$1,$BG$12:$BN$12,0)),0)+IF(AND($BG$2=BG2,$BH$2=BH2,$BF$2&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$2,$BG$12:$BN$12,0)),0)+IF(AND($BG$3=BG2,$BH$3=BH2,$BF$3&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$3,$BG$12:$BN$12,0)),0)+IF(AND($BG$4=BG2,$BH$4=BH2,$BF$4&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$4,$BG$12:$BN$12,0)),0)+IF(AND($BG$5=BG2,$BH$5=BH2,$BF$5&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$5,$BG$12:$BN$12,0)),0)+IF(AND($BG$6=BG2,$BH$6=BH2,$BF$6&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$6,$BG$12:$BN$12,0)),0)+IF(AND($BG$7=BG2,$BH$7=BH2,$BF$7&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$7,$BG$12:$BN$12,0)),0)+IF(AND($BG$8=BG2,$BH$8=BH2,$BF$8&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$8,$BG$12:$BN$12,0)),0)</f>
         <v>0</v>
       </c>
       <c r="BJ2" s="25">
-        <f t="shared" ref="BJ2:BJ8" si="3">IF(COUNTIFS($BG$1:$BG$8,BG2,$BH$1:$BH$8,BH2)&lt;=1,0,SUMPRODUCT(INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),0)*TRANSPOSE(($BG$1:$BG$8=BG2)*($BH$1:$BH$8=BH2))))</f>
-        <v>0</v>
-      </c>
-      <c r="BK2" s="100">
+        <f t="shared" ref="BJ2:BJ8" si="3">IF(AND($BG$1=BG2,$BH$1=BH2,$BF$1&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$1,$BG$24:$BN$24,0)),0)+IF(AND($BG$2=BG2,$BH$2=BH2,$BF$2&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$2,$BG$24:$BN$24,0)),0)+IF(AND($BG$3=BG2,$BH$3=BH2,$BF$3&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$3,$BG$24:$BN$24,0)),0)+IF(AND($BG$4=BG2,$BH$4=BH2,$BF$4&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$4,$BG$24:$BN$24,0)),0)+IF(AND($BG$5=BG2,$BH$5=BH2,$BF$5&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$5,$BG$24:$BN$24,0)),0)+IF(AND($BG$6=BG2,$BH$6=BH2,$BF$6&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$6,$BG$24:$BN$24,0)),0)+IF(AND($BG$7=BG2,$BH$7=BH2,$BF$7&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$7,$BG$24:$BN$24,0)),0)+IF(AND($BG$8=BG2,$BH$8=BH2,$BF$8&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$8,$BG$24:$BN$24,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK2" s="56">
         <f t="shared" ref="BK2:BK8" si="4">1+SUMPRODUCT(--($BG$1:$BG$8&gt;BG2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8&gt;BH2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8=BH2),--($BI$1:$BI$8&gt;BI2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8=BH2),--($BI$1:$BI$8=BI2),--($BF$1:$BF$8&lt;BF2))</f>
         <v>4</v>
       </c>
@@ -5263,11 +5297,11 @@
         <v>TLPH</v>
       </c>
       <c r="C3" s="29">
-        <f>SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
+        <f t="shared" ref="C3:C10" si="5">SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
         <v>8</v>
       </c>
       <c r="D3" s="29">
-        <f>SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
+        <f t="shared" ref="D3:D10" si="6">SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
         <v>2</v>
       </c>
       <c r="E3" s="29">
@@ -5275,23 +5309,23 @@
         <v>17</v>
       </c>
       <c r="F3" s="29">
-        <f>SUMIF($C$14:$C$22,$B3,$E$14:$E$22)+SUMIF($F$14:$F$22,$B3,$D$14:$D$22)+SUMIF($I$14:$I$22,$B3,$K$14:$K$22)+SUMIF($L$14:$L$22,$B3,$J$14:$J$22)+SUMIF($O$14:$O$22,$B3,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B3,$P$14:$P$22)+SUMIF($C$25:$C$33,$B3,$E$25:$E$33)+SUMIF($F$25:$F$33,$B3,$D$25:$D$33)+SUMIF($I$25:$I$33,$B3,$K$25:$K$33)+SUMIF($L$25:$L$33,$B3,$J$25:$J$33)+SUMIF($O$25:$O$33,$B3,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B3,$P$25:$P$33)+SUMIF($C$36:$C$44,$B3,$E$36:$E$44)+SUMIF($F$36:$F$44,$B3,$D$36:$D$44)+SUMIF($I$36:$I$44,$B3,$K$36:$K$44)+SUMIF($L$36:$L$44,$B3,$J$36:$J$44)+SUMIF($O$36:$O$44,$B3,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B3,$P$36:$P$44)+SUMIF($C$47:$C$55,$B3,$E$47:$E$55)+SUMIF($F$47:$F$55,$B3,$D$47:$D$55)</f>
+        <f t="shared" ref="F3:F10" si="7">SUMIF($C$14:$C$22,$B3,$E$14:$E$22)+SUMIF($F$14:$F$22,$B3,$D$14:$D$22)+SUMIF($I$14:$I$22,$B3,$K$14:$K$22)+SUMIF($L$14:$L$22,$B3,$J$14:$J$22)+SUMIF($O$14:$O$22,$B3,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B3,$P$14:$P$22)+SUMIF($C$25:$C$33,$B3,$E$25:$E$33)+SUMIF($F$25:$F$33,$B3,$D$25:$D$33)+SUMIF($I$25:$I$33,$B3,$K$25:$K$33)+SUMIF($L$25:$L$33,$B3,$J$25:$J$33)+SUMIF($O$25:$O$33,$B3,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B3,$P$25:$P$33)+SUMIF($C$36:$C$44,$B3,$E$36:$E$44)+SUMIF($F$36:$F$44,$B3,$D$36:$D$44)+SUMIF($I$36:$I$44,$B3,$K$36:$K$44)+SUMIF($L$36:$L$44,$B3,$J$36:$J$44)+SUMIF($O$36:$O$44,$B3,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B3,$P$36:$P$44)+SUMIF($C$47:$C$55,$B3,$E$47:$E$55)+SUMIF($F$47:$F$55,$B3,$D$47:$D$55)</f>
         <v>5</v>
       </c>
       <c r="G3" s="30">
-        <f t="shared" ref="G3:G11" si="5">E3-F3</f>
+        <f t="shared" ref="G3:G10" si="8">E3-F3</f>
         <v>12</v>
       </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="61"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="97"/>
       <c r="BF3" s="25" t="s">
         <v>52</v>
       </c>
@@ -5311,7 +5345,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BK3" s="100">
+      <c r="BK3" s="56">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -5322,15 +5356,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="28" t="str">
-        <f t="shared" ref="B4:B10" si="6">INDEX($BF$1:$BF$8,MATCH(ROW()-2,$BK$1:$BK$8,0))</f>
+        <f t="shared" ref="B4:B10" si="9">INDEX($BF$1:$BF$8,MATCH(ROW()-2,$BK$1:$BK$8,0))</f>
         <v>T. FLCP</v>
       </c>
       <c r="C4" s="29">
-        <f>SUMPRODUCT(($C$14:$C$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="D4" s="29">
-        <f>SUMPRODUCT(($C$14:$C$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E4" s="29">
@@ -5338,23 +5372,23 @@
         <v>15</v>
       </c>
       <c r="F4" s="29">
-        <f>SUMIF($C$14:$C$22,$B4,$E$14:$E$22)+SUMIF($F$14:$F$22,$B4,$D$14:$D$22)+SUMIF($I$14:$I$22,$B4,$K$14:$K$22)+SUMIF($L$14:$L$22,$B4,$J$14:$J$22)+SUMIF($O$14:$O$22,$B4,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B4,$P$14:$P$22)+SUMIF($C$25:$C$33,$B4,$E$25:$E$33)+SUMIF($F$25:$F$33,$B4,$D$25:$D$33)+SUMIF($I$25:$I$33,$B4,$K$25:$K$33)+SUMIF($L$25:$L$33,$B4,$J$25:$J$33)+SUMIF($O$25:$O$33,$B4,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B4,$P$25:$P$33)+SUMIF($C$36:$C$44,$B4,$E$36:$E$44)+SUMIF($F$36:$F$44,$B4,$D$36:$D$44)+SUMIF($I$36:$I$44,$B4,$K$36:$K$44)+SUMIF($L$36:$L$44,$B4,$J$36:$J$44)+SUMIF($O$36:$O$44,$B4,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B4,$P$36:$P$44)+SUMIF($C$47:$C$55,$B4,$E$47:$E$55)+SUMIF($F$47:$F$55,$B4,$D$47:$D$55)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G4" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="61"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="97"/>
       <c r="BF4" s="25" t="s">
         <v>53</v>
       </c>
@@ -5374,50 +5408,50 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BK4" s="100">
+      <c r="BK4" s="56">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="BL4" s="25"/>
     </row>
     <row r="5" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="101">
+      <c r="A5" s="57">
         <v>3</v>
       </c>
-      <c r="B5" s="102" t="str">
+      <c r="B5" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>ONIC PH</v>
+      </c>
+      <c r="C5" s="59">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="D5" s="59">
         <f t="shared" si="6"/>
-        <v>ONIC PH</v>
-      </c>
-      <c r="C5" s="103">
-        <f>SUMPRODUCT(($C$14:$C$22=$B5)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B5)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B5)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B5)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B5)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B5)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B5)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B5)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B5)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B5)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B5)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B5)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B5)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B5)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B5)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B5)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B5)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B5)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>7</v>
-      </c>
-      <c r="D5" s="103">
-        <f>SUMPRODUCT(($C$14:$C$22=$B5)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B5)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B5)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B5)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B5)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B5)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B5)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B5)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B5)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B5)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B5)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B5)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B5)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B5)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B5)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B5)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B5)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B5)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
-        <v>2</v>
-      </c>
-      <c r="E5" s="103">
+        <v>2</v>
+      </c>
+      <c r="E5" s="59">
         <f>SUMIF($C$14:$C$22,$B5,$D$14:$D$22)+SUMIF($F$14:$F$22,$B5,$E$14:$E$22)+SUMIF($I$14:$I$22,$B5,$J$14:$J$22)+SUMIF($L$14:$L$22,$B5,$K$14:$K$22)+SUMIF($O$14:$O$22,$B5,$P$14:$P$22)+SUMIF($R$14:$R$22,$B5,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B5,$D$25:$D$33)+SUMIF($F$25:$F$33,$B5,$E$25:$E$33)+SUMIF($I$25:$I$33,$B5,$J$25:$J$33)+SUMIF($L$25:$L$33,$B5,$K$25:$K$33)+SUMIF($O$25:$O$33,$B5,$P$25:$P$33)+SUMIF($R$25:$R$33,$B5,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B5,$D$36:$D$44)+SUMIF($F$36:$F$44,$B5,$E$36:$E$44)+SUMIF($I$36:$I$44,$B5,$J$36:$J$44)+SUMIF($L$36:$L$44,$B5,$K$36:$K$44)+SUMIF($O$36:$O$44,$B5,$P$36:$P$44)+SUMIF($R$36:$R$44,$B5,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
         <v>15</v>
       </c>
-      <c r="F5" s="103">
-        <f>SUMIF($C$14:$C$22,$B5,$E$14:$E$22)+SUMIF($F$14:$F$22,$B5,$D$14:$D$22)+SUMIF($I$14:$I$22,$B5,$K$14:$K$22)+SUMIF($L$14:$L$22,$B5,$J$14:$J$22)+SUMIF($O$14:$O$22,$B5,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B5,$P$14:$P$22)+SUMIF($C$25:$C$33,$B5,$E$25:$E$33)+SUMIF($F$25:$F$33,$B5,$D$25:$D$33)+SUMIF($I$25:$I$33,$B5,$K$25:$K$33)+SUMIF($L$25:$L$33,$B5,$J$25:$J$33)+SUMIF($O$25:$O$33,$B5,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B5,$P$25:$P$33)+SUMIF($C$36:$C$44,$B5,$E$36:$E$44)+SUMIF($F$36:$F$44,$B5,$D$36:$D$44)+SUMIF($I$36:$I$44,$B5,$K$36:$K$44)+SUMIF($L$36:$L$44,$B5,$J$36:$J$44)+SUMIF($O$36:$O$44,$B5,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B5,$P$36:$P$44)+SUMIF($C$47:$C$55,$B5,$E$47:$E$55)+SUMIF($F$47:$F$55,$B5,$D$47:$D$55)</f>
+      <c r="F5" s="59">
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="G5" s="104">
-        <f t="shared" si="5"/>
+      <c r="G5" s="60">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="I5" s="59"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="61"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="97"/>
       <c r="BF5" s="25" t="s">
         <v>56</v>
       </c>
@@ -5437,7 +5471,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BK5" s="100">
+      <c r="BK5" s="56">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -5448,15 +5482,15 @@
         <v>4</v>
       </c>
       <c r="B6" s="46" t="str">
+        <f t="shared" si="9"/>
+        <v>AUR PH</v>
+      </c>
+      <c r="C6" s="51">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="D6" s="51">
         <f t="shared" si="6"/>
-        <v>AUR PH</v>
-      </c>
-      <c r="C6" s="51">
-        <f>SUMPRODUCT(($C$14:$C$22=$B6)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B6)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B6)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B6)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B6)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B6)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B6)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B6)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B6)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B6)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B6)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B6)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B6)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B6)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B6)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B6)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B6)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B6)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>5</v>
-      </c>
-      <c r="D6" s="51">
-        <f>SUMPRODUCT(($C$14:$C$22=$B6)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B6)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B6)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B6)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B6)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B6)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B6)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B6)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B6)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B6)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B6)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B6)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B6)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B6)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B6)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B6)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B6)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B6)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
         <v>4</v>
       </c>
       <c r="E6" s="51">
@@ -5464,23 +5498,23 @@
         <v>12</v>
       </c>
       <c r="F6" s="51">
-        <f>SUMIF($C$14:$C$22,$B6,$E$14:$E$22)+SUMIF($F$14:$F$22,$B6,$D$14:$D$22)+SUMIF($I$14:$I$22,$B6,$K$14:$K$22)+SUMIF($L$14:$L$22,$B6,$J$14:$J$22)+SUMIF($O$14:$O$22,$B6,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B6,$P$14:$P$22)+SUMIF($C$25:$C$33,$B6,$E$25:$E$33)+SUMIF($F$25:$F$33,$B6,$D$25:$D$33)+SUMIF($I$25:$I$33,$B6,$K$25:$K$33)+SUMIF($L$25:$L$33,$B6,$J$25:$J$33)+SUMIF($O$25:$O$33,$B6,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B6,$P$25:$P$33)+SUMIF($C$36:$C$44,$B6,$E$36:$E$44)+SUMIF($F$36:$F$44,$B6,$D$36:$D$44)+SUMIF($I$36:$I$44,$B6,$K$36:$K$44)+SUMIF($L$36:$L$44,$B6,$J$36:$J$44)+SUMIF($O$36:$O$44,$B6,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B6,$P$36:$P$44)+SUMIF($C$47:$C$55,$B6,$E$47:$E$55)+SUMIF($F$47:$F$55,$B6,$D$47:$D$55)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="G6" s="52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="61"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
       <c r="BF6" s="25" t="s">
         <v>54</v>
       </c>
@@ -5500,7 +5534,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BK6" s="100">
+      <c r="BK6" s="56">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5511,15 +5545,15 @@
         <v>5</v>
       </c>
       <c r="B7" s="46" t="str">
+        <f t="shared" si="9"/>
+        <v>OMEGA</v>
+      </c>
+      <c r="C7" s="51">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="51">
         <f t="shared" si="6"/>
-        <v>OMEGA</v>
-      </c>
-      <c r="C7" s="51">
-        <f>SUMPRODUCT(($C$14:$C$22=$B7)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B7)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B7)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B7)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B7)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B7)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B7)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B7)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B7)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B7)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B7)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B7)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B7)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B7)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B7)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B7)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B7)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B7)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>4</v>
-      </c>
-      <c r="D7" s="51">
-        <f>SUMPRODUCT(($C$14:$C$22=$B7)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B7)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B7)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B7)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B7)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B7)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B7)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B7)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B7)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B7)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B7)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B7)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B7)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B7)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B7)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B7)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B7)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B7)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
         <v>6</v>
       </c>
       <c r="E7" s="51">
@@ -5527,23 +5561,23 @@
         <v>9</v>
       </c>
       <c r="F7" s="51">
-        <f>SUMIF($C$14:$C$22,$B7,$E$14:$E$22)+SUMIF($F$14:$F$22,$B7,$D$14:$D$22)+SUMIF($I$14:$I$22,$B7,$K$14:$K$22)+SUMIF($L$14:$L$22,$B7,$J$14:$J$22)+SUMIF($O$14:$O$22,$B7,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B7,$P$14:$P$22)+SUMIF($C$25:$C$33,$B7,$E$25:$E$33)+SUMIF($F$25:$F$33,$B7,$D$25:$D$33)+SUMIF($I$25:$I$33,$B7,$K$25:$K$33)+SUMIF($L$25:$L$33,$B7,$J$25:$J$33)+SUMIF($O$25:$O$33,$B7,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B7,$P$25:$P$33)+SUMIF($C$36:$C$44,$B7,$E$36:$E$44)+SUMIF($F$36:$F$44,$B7,$D$36:$D$44)+SUMIF($I$36:$I$44,$B7,$K$36:$K$44)+SUMIF($L$36:$L$44,$B7,$J$36:$J$44)+SUMIF($O$36:$O$44,$B7,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B7,$P$36:$P$44)+SUMIF($C$47:$C$55,$B7,$E$47:$E$55)+SUMIF($F$47:$F$55,$B7,$D$47:$D$55)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="G7" s="52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-7</v>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="61"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="97"/>
       <c r="BF7" s="25" t="s">
         <v>55</v>
       </c>
@@ -5563,50 +5597,50 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BK7" s="100">
+      <c r="BK7" s="56">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="BL7" s="25"/>
     </row>
     <row r="8" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="101">
+      <c r="A8" s="57">
         <v>6</v>
       </c>
-      <c r="B8" s="102" t="str">
+      <c r="B8" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>TNC</v>
+      </c>
+      <c r="C8" s="59">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="D8" s="59">
         <f t="shared" si="6"/>
-        <v>TNC</v>
-      </c>
-      <c r="C8" s="103">
-        <f>SUMPRODUCT(($C$14:$C$22=$B8)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B8)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B8)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B8)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B8)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B8)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B8)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B8)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B8)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B8)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B8)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B8)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B8)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B8)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B8)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B8)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B8)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B8)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>3</v>
-      </c>
-      <c r="D8" s="103">
-        <f>SUMPRODUCT(($C$14:$C$22=$B8)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B8)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B8)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B8)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B8)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B8)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B8)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B8)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B8)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B8)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B8)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B8)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B8)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B8)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B8)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B8)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B8)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B8)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
         <v>6</v>
       </c>
-      <c r="E8" s="103">
+      <c r="E8" s="59">
         <f>SUMIF($C$14:$C$22,$B8,$D$14:$D$22)+SUMIF($F$14:$F$22,$B8,$E$14:$E$22)+SUMIF($I$14:$I$22,$B8,$J$14:$J$22)+SUMIF($L$14:$L$22,$B8,$K$14:$K$22)+SUMIF($O$14:$O$22,$B8,$P$14:$P$22)+SUMIF($R$14:$R$22,$B8,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B8,$D$25:$D$33)+SUMIF($F$25:$F$33,$B8,$E$25:$E$33)+SUMIF($I$25:$I$33,$B8,$J$25:$J$33)+SUMIF($L$25:$L$33,$B8,$K$25:$K$33)+SUMIF($O$25:$O$33,$B8,$P$25:$P$33)+SUMIF($R$25:$R$33,$B8,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B8,$D$36:$D$44)+SUMIF($F$36:$F$44,$B8,$E$36:$E$44)+SUMIF($I$36:$I$44,$B8,$J$36:$J$44)+SUMIF($L$36:$L$44,$B8,$K$36:$K$44)+SUMIF($O$36:$O$44,$B8,$P$36:$P$44)+SUMIF($R$36:$R$44,$B8,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B6,$D$47:$D$55)+SUMIF($F$47:$F$55,$B6,$E$47:$E$55)</f>
         <v>9</v>
       </c>
-      <c r="F8" s="103">
-        <f>SUMIF($C$14:$C$22,$B8,$E$14:$E$22)+SUMIF($F$14:$F$22,$B8,$D$14:$D$22)+SUMIF($I$14:$I$22,$B8,$K$14:$K$22)+SUMIF($L$14:$L$22,$B8,$J$14:$J$22)+SUMIF($O$14:$O$22,$B8,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B8,$P$14:$P$22)+SUMIF($C$25:$C$33,$B8,$E$25:$E$33)+SUMIF($F$25:$F$33,$B8,$D$25:$D$33)+SUMIF($I$25:$I$33,$B8,$K$25:$K$33)+SUMIF($L$25:$L$33,$B8,$J$25:$J$33)+SUMIF($O$25:$O$33,$B8,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B8,$P$25:$P$33)+SUMIF($C$36:$C$44,$B8,$E$36:$E$44)+SUMIF($F$36:$F$44,$B8,$D$36:$D$44)+SUMIF($I$36:$I$44,$B8,$K$36:$K$44)+SUMIF($L$36:$L$44,$B8,$J$36:$J$44)+SUMIF($O$36:$O$44,$B8,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B8,$P$36:$P$44)+SUMIF($C$47:$C$55,$B8,$E$47:$E$55)+SUMIF($F$47:$F$55,$B8,$D$47:$D$55)</f>
+      <c r="F8" s="59">
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="G8" s="104">
-        <f t="shared" si="5"/>
+      <c r="G8" s="60">
+        <f t="shared" si="8"/>
         <v>-5</v>
       </c>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="61"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="97"/>
       <c r="BF8" s="25" t="s">
         <v>57</v>
       </c>
@@ -5626,26 +5660,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BK8" s="100">
+      <c r="BK8" s="56">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="BL8" s="25"/>
     </row>
     <row r="9" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="105">
+      <c r="A9" s="61">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="str">
+      <c r="B9" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>AP.BREN</v>
+      </c>
+      <c r="C9" s="39">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="D9" s="39">
         <f t="shared" si="6"/>
-        <v>AP.BREN</v>
-      </c>
-      <c r="C9" s="39">
-        <f>SUMPRODUCT(($C$14:$C$22=$B9)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B9)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B9)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B9)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B9)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B9)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B9)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B9)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B9)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B9)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B9)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B9)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B9)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B9)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B9)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B9)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B9)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B9)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>3</v>
-      </c>
-      <c r="D9" s="39">
-        <f>SUMPRODUCT(($C$14:$C$22=$B9)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B9)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B9)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B9)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B9)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B9)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B9)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B9)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B9)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B9)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B9)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B9)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B9)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B9)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B9)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B9)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B9)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B9)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
         <v>7</v>
       </c>
       <c r="E9" s="39">
@@ -5653,23 +5687,23 @@
         <v>9</v>
       </c>
       <c r="F9" s="39">
-        <f>SUMIF($C$14:$C$22,$B9,$E$14:$E$22)+SUMIF($F$14:$F$22,$B9,$D$14:$D$22)+SUMIF($I$14:$I$22,$B9,$K$14:$K$22)+SUMIF($L$14:$L$22,$B9,$J$14:$J$22)+SUMIF($O$14:$O$22,$B9,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B9,$P$14:$P$22)+SUMIF($C$25:$C$33,$B9,$E$25:$E$33)+SUMIF($F$25:$F$33,$B9,$D$25:$D$33)+SUMIF($I$25:$I$33,$B9,$K$25:$K$33)+SUMIF($L$25:$L$33,$B9,$J$25:$J$33)+SUMIF($O$25:$O$33,$B9,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B9,$P$25:$P$33)+SUMIF($C$36:$C$44,$B9,$E$36:$E$44)+SUMIF($F$36:$F$44,$B9,$D$36:$D$44)+SUMIF($I$36:$I$44,$B9,$K$36:$K$44)+SUMIF($L$36:$L$44,$B9,$J$36:$J$44)+SUMIF($O$36:$O$44,$B9,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B9,$P$36:$P$44)+SUMIF($C$47:$C$55,$B9,$E$47:$E$55)+SUMIF($F$47:$F$55,$B9,$D$47:$D$55)</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="G9" s="106">
-        <f t="shared" si="5"/>
+      <c r="G9" s="62">
+        <f t="shared" si="8"/>
         <v>-6</v>
       </c>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="61"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="97"/>
       <c r="BF9" s="25"/>
       <c r="BG9" s="25"/>
       <c r="BH9" s="25"/>
@@ -5678,19 +5712,19 @@
       <c r="BL9" s="25"/>
     </row>
     <row r="10" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="105">
+      <c r="A10" s="61">
         <v>8</v>
       </c>
-      <c r="B10" s="96" t="str">
+      <c r="B10" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>TWIS PH</v>
+      </c>
+      <c r="C10" s="39">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="39">
         <f t="shared" si="6"/>
-        <v>TWIS PH</v>
-      </c>
-      <c r="C10" s="39">
-        <f>SUMPRODUCT(($C$14:$C$22=$B10)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B10)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B10)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B10)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B10)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B10)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B10)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B10)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B10)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B10)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B10)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B10)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B10)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B10)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B10)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B10)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B10)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B10)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="39">
-        <f>SUMPRODUCT(($C$14:$C$22=$B10)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B10)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B10)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B10)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B10)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B10)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B10)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B10)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B10)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B10)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B10)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B10)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B10)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B10)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B10)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B10)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B10)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B10)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
         <v>9</v>
       </c>
       <c r="E10" s="39">
@@ -5698,34 +5732,34 @@
         <v>2</v>
       </c>
       <c r="F10" s="39">
-        <f>SUMIF($C$14:$C$22,$B10,$E$14:$E$22)+SUMIF($F$14:$F$22,$B10,$D$14:$D$22)+SUMIF($I$14:$I$22,$B10,$K$14:$K$22)+SUMIF($L$14:$L$22,$B10,$J$14:$J$22)+SUMIF($O$14:$O$22,$B10,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B10,$P$14:$P$22)+SUMIF($C$25:$C$33,$B10,$E$25:$E$33)+SUMIF($F$25:$F$33,$B10,$D$25:$D$33)+SUMIF($I$25:$I$33,$B10,$K$25:$K$33)+SUMIF($L$25:$L$33,$B10,$J$25:$J$33)+SUMIF($O$25:$O$33,$B10,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B10,$P$25:$P$33)+SUMIF($C$36:$C$44,$B10,$E$36:$E$44)+SUMIF($F$36:$F$44,$B10,$D$36:$D$44)+SUMIF($I$36:$I$44,$B10,$K$36:$K$44)+SUMIF($L$36:$L$44,$B10,$J$36:$J$44)+SUMIF($O$36:$O$44,$B10,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B10,$P$36:$P$44)+SUMIF($C$47:$C$55,$B10,$E$47:$E$55)+SUMIF($F$47:$F$55,$B10,$D$47:$D$55)</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="G10" s="106">
-        <f t="shared" si="5"/>
+      <c r="G10" s="62">
+        <f t="shared" si="8"/>
         <v>-16</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="64"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="100"/>
     </row>
     <row r="11" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="107"/>
-      <c r="B11" s="108"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
       <c r="C11" s="40"/>
       <c r="D11" s="40"/>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
-      <c r="G11" s="109"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="BG12" t="str">
@@ -5762,27 +5796,27 @@
       </c>
     </row>
     <row r="13" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="67"/>
-      <c r="H13" s="65" t="s">
+      <c r="B13" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="88"/>
+      <c r="H13" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="66"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="67"/>
-      <c r="N13" s="65" t="s">
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="88"/>
+      <c r="N13" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="67"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
       <c r="BF13" s="25" t="str">
         <f>BF1</f>
         <v>AP.BREN</v>
@@ -5792,31 +5826,31 @@
         <v>0</v>
       </c>
       <c r="BH13">
-        <f t="shared" ref="BH13:BO21" si="7">SUMPRODUCT(($C$14:$C$22=$BF13)*($F$14:$F$22=BH$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF13)*($C$14:$C$22=BH$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF13)*($L$14:$L$22=BH$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF13)*($I$14:$I$22=BH$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF13)*($R$14:$R$22=BH$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF13)*($O$14:$O$22=BH$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF13)*($F$25:$F$33=BH$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF13)*($C$25:$C$33=BH$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF13)*($L$25:$L$33=BH$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF13)*($I$25:$I$33=BH$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF13)*($R$25:$R$33=BH$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF13)*($O$25:$O$33=BH$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF13)*($F$37:$F$45=BH$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF13)*($C$37:$C$45=BH$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF13)*($L$37:$L$45=BH$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF13)*($I$37:$I$45=BH$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF13)*($R$37:$R$45=BH$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF13)*($O$37:$O$45=BH$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
+        <f t="shared" ref="BH13:BN20" si="10">SUMPRODUCT(($C$14:$C$22=$BF13)*($F$14:$F$22=BH$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF13)*($C$14:$C$22=BH$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF13)*($L$14:$L$22=BH$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF13)*($I$14:$I$22=BH$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF13)*($R$14:$R$22=BH$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF13)*($O$14:$O$22=BH$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF13)*($F$25:$F$33=BH$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF13)*($C$25:$C$33=BH$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF13)*($L$25:$L$33=BH$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF13)*($I$25:$I$33=BH$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF13)*($R$25:$R$33=BH$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF13)*($O$25:$O$33=BH$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF13)*($F$37:$F$45=BH$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF13)*($C$37:$C$45=BH$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF13)*($L$37:$L$45=BH$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF13)*($I$37:$I$45=BH$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF13)*($R$37:$R$45=BH$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF13)*($O$37:$O$45=BH$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
         <v>0</v>
       </c>
       <c r="BI13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BM13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BN13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -5867,39 +5901,39 @@
         <v>58</v>
       </c>
       <c r="BF14" s="25" t="str">
-        <f t="shared" ref="BF14:BF21" si="8">BF2</f>
+        <f t="shared" ref="BF14:BF20" si="11">BF2</f>
         <v>AUR PH</v>
       </c>
       <c r="BG14">
-        <f t="shared" ref="BG14:BG21" si="9">SUMPRODUCT(($C$14:$C$22=$BF14)*($F$14:$F$22=BG$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF14)*($C$14:$C$22=BG$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF14)*($L$14:$L$22=BG$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF14)*($I$14:$I$22=BG$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF14)*($R$14:$R$22=BG$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF14)*($O$14:$O$22=BG$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF14)*($F$25:$F$33=BG$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF14)*($C$25:$C$33=BG$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF14)*($L$25:$L$33=BG$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF14)*($I$25:$I$33=BG$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF14)*($R$25:$R$33=BG$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF14)*($O$25:$O$33=BG$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF14)*($F$37:$F$45=BG$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF14)*($C$37:$C$45=BG$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF14)*($L$37:$L$45=BG$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF14)*($I$37:$I$45=BG$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF14)*($R$37:$R$45=BG$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF14)*($O$37:$O$45=BG$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
+        <f t="shared" ref="BG14:BG20" si="12">SUMPRODUCT(($C$14:$C$22=$BF14)*($F$14:$F$22=BG$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF14)*($C$14:$C$22=BG$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF14)*($L$14:$L$22=BG$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF14)*($I$14:$I$22=BG$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF14)*($R$14:$R$22=BG$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF14)*($O$14:$O$22=BG$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF14)*($F$25:$F$33=BG$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF14)*($C$25:$C$33=BG$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF14)*($L$25:$L$33=BG$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF14)*($I$25:$I$33=BG$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF14)*($R$25:$R$33=BG$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF14)*($O$25:$O$33=BG$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF14)*($F$37:$F$45=BG$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF14)*($C$37:$C$45=BG$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF14)*($L$37:$L$45=BG$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF14)*($I$37:$I$45=BG$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF14)*($R$37:$R$45=BG$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF14)*($O$37:$O$45=BG$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
         <v>1</v>
       </c>
       <c r="BH14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BI14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="BJ14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BN14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5944,39 +5978,39 @@
         <v>53</v>
       </c>
       <c r="BF15" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>OMEGA</v>
       </c>
       <c r="BG15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BH15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BI15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BL15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BM15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BN15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5997,39 +6031,39 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="6"/>
       <c r="BF16" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>ONIC PH</v>
       </c>
       <c r="BG16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="BH16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BI16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="BJ16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BM16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BN16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6080,39 +6114,39 @@
         <v>51</v>
       </c>
       <c r="BF17" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>T. FLCP</v>
       </c>
       <c r="BG17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BH17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BI17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BK17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BN17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -6157,39 +6191,39 @@
         <v>54</v>
       </c>
       <c r="BF18" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>TLPH</v>
       </c>
       <c r="BG18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BH18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BI18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="BJ18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BK18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BM18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="BN18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6234,39 +6268,39 @@
         <v>56</v>
       </c>
       <c r="BF19" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>TNC</v>
       </c>
       <c r="BG19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BH19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BI19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BM19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BN19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6317,39 +6351,39 @@
         <v>57</v>
       </c>
       <c r="BF20" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>TWIS PH</v>
       </c>
       <c r="BG20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BH20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BI20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BL20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BM20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BN20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -6413,27 +6447,27 @@
       <c r="R22" s="6"/>
     </row>
     <row r="24" spans="2:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="65" t="s">
+      <c r="B24" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="67"/>
-      <c r="H24" s="65" t="s">
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="88"/>
+      <c r="H24" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="67"/>
-      <c r="N24" s="65" t="s">
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="88"/>
+      <c r="N24" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="67"/>
+      <c r="O24" s="87"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
       <c r="BG24" t="str">
         <f>BF25</f>
         <v>AP.BREN</v>
@@ -6522,31 +6556,31 @@
         <v>0</v>
       </c>
       <c r="BH25">
-        <f t="shared" ref="BH25:BN32" si="10">SUMPRODUCT(($C$14:$C$22=$BF25)*($F$14:$F$22=BH$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF25)*($C$14:$C$22=BH$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF25)*($L$14:$L$22=BH$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF25)*($I$14:$I$22=BH$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF25)*($R$14:$R$22=BH$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF25)*($O$14:$O$22=BH$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF25)*($F$25:$F$33=BH$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF25)*($C$25:$C$33=BH$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF25)*($L$25:$L$33=BH$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF25)*($I$25:$I$33=BH$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF25)*($R$25:$R$33=BH$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF25)*($O$25:$O$33=BH$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF25)*($F$36:$F$44=BH$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF25)*($C$36:$C$44=BH$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF25)*($L$36:$L$44=BH$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF25)*($I$36:$I$44=BH$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF25)*($R$36:$R$44=BH$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF25)*($O$36:$O$44=BH$24)*$Q$36:$Q$44)</f>
+        <f t="shared" ref="BH25:BN32" si="13">SUMPRODUCT(($C$14:$C$22=$BF25)*($F$14:$F$22=BH$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF25)*($C$14:$C$22=BH$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF25)*($L$14:$L$22=BH$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF25)*($I$14:$I$22=BH$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF25)*($R$14:$R$22=BH$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF25)*($O$14:$O$22=BH$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF25)*($F$25:$F$33=BH$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF25)*($C$25:$C$33=BH$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF25)*($L$25:$L$33=BH$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF25)*($I$25:$I$33=BH$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF25)*($R$25:$R$33=BH$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF25)*($O$25:$O$33=BH$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF25)*($F$36:$F$44=BH$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF25)*($C$36:$C$44=BH$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF25)*($L$36:$L$44=BH$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF25)*($I$36:$I$44=BH$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF25)*($R$36:$R$44=BH$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF25)*($O$36:$O$44=BH$24)*$Q$36:$Q$44)</f>
         <v>0</v>
       </c>
       <c r="BI25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BJ25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BK25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BL25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BM25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="BN25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -6591,39 +6625,39 @@
         <v>53</v>
       </c>
       <c r="BF26" s="25" t="str">
-        <f t="shared" ref="BF26:BF32" si="11">BF14</f>
+        <f t="shared" ref="BF26:BF32" si="14">BF14</f>
         <v>AUR PH</v>
       </c>
       <c r="BG26">
-        <f t="shared" ref="BG26:BG32" si="12">SUMPRODUCT(($C$14:$C$22=$BF26)*($F$14:$F$22=BG$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF26)*($C$14:$C$22=BG$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF26)*($L$14:$L$22=BG$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF26)*($I$14:$I$22=BG$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF26)*($R$14:$R$22=BG$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF26)*($O$14:$O$22=BG$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF26)*($F$25:$F$33=BG$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF26)*($C$25:$C$33=BG$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF26)*($L$25:$L$33=BG$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF26)*($I$25:$I$33=BG$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF26)*($R$25:$R$33=BG$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF26)*($O$25:$O$33=BG$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF26)*($F$36:$F$44=BG$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF26)*($C$36:$C$44=BG$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF26)*($L$36:$L$44=BG$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF26)*($I$36:$I$44=BG$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF26)*($R$36:$R$44=BG$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF26)*($O$36:$O$44=BG$24)*$Q$36:$Q$44)</f>
+        <f t="shared" ref="BG26:BG32" si="15">SUMPRODUCT(($C$14:$C$22=$BF26)*($F$14:$F$22=BG$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF26)*($C$14:$C$22=BG$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF26)*($L$14:$L$22=BG$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF26)*($I$14:$I$22=BG$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF26)*($R$14:$R$22=BG$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF26)*($O$14:$O$22=BG$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF26)*($F$25:$F$33=BG$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF26)*($C$25:$C$33=BG$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF26)*($L$25:$L$33=BG$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF26)*($I$25:$I$33=BG$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF26)*($R$25:$R$33=BG$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF26)*($O$25:$O$33=BG$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF26)*($F$36:$F$44=BG$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF26)*($C$36:$C$44=BG$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF26)*($L$36:$L$44=BG$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF26)*($I$36:$I$44=BG$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF26)*($R$36:$R$44=BG$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF26)*($O$36:$O$44=BG$24)*$Q$36:$Q$44)</f>
         <v>2</v>
       </c>
       <c r="BH26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BI26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="BJ26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BK26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BL26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BM26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BN26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -6644,39 +6678,39 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="6"/>
       <c r="BF27" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>OMEGA</v>
       </c>
       <c r="BG27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="BH27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BI27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BJ27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BK27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BL27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BM27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BN27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -6723,39 +6757,39 @@
         <v>57</v>
       </c>
       <c r="BF28" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>ONIC PH</v>
       </c>
       <c r="BG28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="BH28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BI28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="BJ28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BK28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BL28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BM28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BN28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -6796,39 +6830,39 @@
         <v>58</v>
       </c>
       <c r="BF29" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>T. FLCP</v>
       </c>
       <c r="BG29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="BH29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BI29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BJ29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BK29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BL29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BM29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BN29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -6869,39 +6903,39 @@
         <v>53</v>
       </c>
       <c r="BF30" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>TLPH</v>
       </c>
       <c r="BG30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="BH30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BI30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="BJ30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BK30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BL30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BM30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="BN30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -6948,39 +6982,39 @@
         <v>55</v>
       </c>
       <c r="BF31" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>TNC</v>
       </c>
       <c r="BG31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="BH31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="BI31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BJ31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BK31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BL31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BM31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BN31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -7021,39 +7055,39 @@
         <v>56</v>
       </c>
       <c r="BF32" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>TWIS PH</v>
       </c>
       <c r="BG32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="BH32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BI32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BJ32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BK32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BL32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BM32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BN32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -7075,27 +7109,27 @@
       <c r="R33" s="6"/>
     </row>
     <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67"/>
-      <c r="H35" s="65" t="s">
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="88"/>
+      <c r="H35" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="67"/>
-      <c r="N35" s="65" t="s">
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="88"/>
+      <c r="N35" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="67"/>
+      <c r="O35" s="87"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="87"/>
+      <c r="R35" s="88"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
@@ -7326,26 +7360,26 @@
     </row>
     <row r="45" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="97" t="s">
+      <c r="B46" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="98"/>
-      <c r="D46" s="98"/>
-      <c r="E46" s="98"/>
-      <c r="F46" s="99"/>
-      <c r="H46" s="85" t="s">
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
+      <c r="H46" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="I46" s="86"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="86"/>
-      <c r="M46" s="86"/>
-      <c r="N46" s="86"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="87"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="69"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="70"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
@@ -7366,15 +7400,15 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="3"/>
-      <c r="H48" s="92" t="s">
+      <c r="H48" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="I48" s="93"/>
-      <c r="J48" s="95" t="s">
+      <c r="I48" s="80"/>
+      <c r="J48" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="K48" s="95"/>
-      <c r="L48" s="95"/>
+      <c r="K48" s="82"/>
+      <c r="L48" s="82"/>
       <c r="R48" s="10"/>
     </row>
     <row r="49" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7390,17 +7424,17 @@
         <v>ONIC PH</v>
       </c>
       <c r="I49" s="37"/>
-      <c r="J49" s="81" t="str">
+      <c r="J49" s="71" t="str">
         <f>B4</f>
         <v>T. FLCP</v>
       </c>
-      <c r="K49" s="82"/>
+      <c r="K49" s="72"/>
       <c r="L49" s="37"/>
-      <c r="M49" s="94" t="s">
+      <c r="M49" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="N49" s="94"/>
-      <c r="O49" s="94"/>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
       <c r="R49" s="10"/>
     </row>
     <row r="50" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7416,23 +7450,23 @@
         <v>TNC</v>
       </c>
       <c r="I50" s="38"/>
-      <c r="J50" s="81" t="str">
+      <c r="J50" s="71" t="str">
         <f>IF(I49&gt;I50, H49, H50)</f>
         <v>TNC</v>
       </c>
-      <c r="K50" s="82"/>
+      <c r="K50" s="72"/>
       <c r="L50" s="38"/>
-      <c r="M50" s="79" t="str">
+      <c r="M50" s="105" t="str">
         <f>IF((L49&gt;L50),J49,J50)</f>
         <v>TNC</v>
       </c>
-      <c r="N50" s="80"/>
+      <c r="N50" s="106"/>
       <c r="O50" s="37"/>
-      <c r="P50" s="90" t="s">
+      <c r="P50" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="Q50" s="90"/>
-      <c r="R50" s="91"/>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="78"/>
     </row>
     <row r="51" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
@@ -7447,23 +7481,23 @@
         <v>AUR PH</v>
       </c>
       <c r="I51" s="37"/>
-      <c r="J51" s="81" t="str">
+      <c r="J51" s="71" t="str">
         <f>B3</f>
         <v>TLPH</v>
       </c>
-      <c r="K51" s="82"/>
+      <c r="K51" s="72"/>
       <c r="L51" s="37"/>
-      <c r="M51" s="79" t="str">
+      <c r="M51" s="105" t="str">
         <f>IF((L51&gt;L52),J51,J52)</f>
         <v>OMEGA</v>
       </c>
-      <c r="N51" s="80"/>
+      <c r="N51" s="106"/>
       <c r="O51" s="38"/>
-      <c r="P51" s="88" t="str">
+      <c r="P51" s="73" t="str">
         <f>IF((O50&gt;O51),M50,M51)</f>
         <v>OMEGA</v>
       </c>
-      <c r="Q51" s="89"/>
+      <c r="Q51" s="74"/>
       <c r="R51" s="44"/>
       <c r="S51" s="9"/>
     </row>
@@ -7480,23 +7514,23 @@
         <v>OMEGA</v>
       </c>
       <c r="I52" s="38"/>
-      <c r="J52" s="81" t="str">
+      <c r="J52" s="71" t="str">
         <f>IF(I51&gt;I52, H51, H52)</f>
         <v>OMEGA</v>
       </c>
-      <c r="K52" s="82"/>
+      <c r="K52" s="72"/>
       <c r="L52" s="38"/>
-      <c r="M52" s="83" t="str">
+      <c r="M52" s="66" t="str">
         <f>IF((O50&lt;O51),M50,M51)</f>
         <v>OMEGA</v>
       </c>
-      <c r="N52" s="84"/>
+      <c r="N52" s="67"/>
       <c r="O52" s="37"/>
-      <c r="P52" s="88" t="str">
+      <c r="P52" s="73" t="str">
         <f>IF((O52&gt;O53),M52,M53)</f>
         <v>OMEGA</v>
       </c>
-      <c r="Q52" s="89"/>
+      <c r="Q52" s="74"/>
       <c r="R52" s="45"/>
       <c r="S52" s="9"/>
     </row>
@@ -7508,21 +7542,21 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="3"/>
-      <c r="H53" s="92" t="s">
+      <c r="H53" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="93"/>
-      <c r="J53" s="73" t="str">
+      <c r="I53" s="80"/>
+      <c r="J53" s="75" t="str">
         <f>IF((L49&lt;L50),J49,J50)</f>
         <v>TNC</v>
       </c>
-      <c r="K53" s="74"/>
+      <c r="K53" s="76"/>
       <c r="L53" s="37"/>
-      <c r="M53" s="83" t="str">
+      <c r="M53" s="66" t="str">
         <f>IF((L53&gt;L54),J53,J54)</f>
         <v>OMEGA</v>
       </c>
-      <c r="N53" s="84"/>
+      <c r="N53" s="67"/>
       <c r="O53" s="38"/>
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
@@ -7537,17 +7571,17 @@
       <c r="E54" s="1"/>
       <c r="F54" s="3"/>
       <c r="H54" s="9"/>
-      <c r="J54" s="73" t="str">
+      <c r="J54" s="75" t="str">
         <f>IF((L51&lt;L52),J51,J52)</f>
         <v>OMEGA</v>
       </c>
-      <c r="K54" s="74"/>
+      <c r="K54" s="76"/>
       <c r="L54" s="38"/>
-      <c r="M54" s="76" t="s">
+      <c r="M54" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="N54" s="77"/>
-      <c r="O54" s="78"/>
+      <c r="N54" s="103"/>
+      <c r="O54" s="104"/>
       <c r="R54" s="10"/>
     </row>
     <row r="55" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7559,11 +7593,11 @@
       <c r="E55" s="5"/>
       <c r="F55" s="6"/>
       <c r="H55" s="9"/>
-      <c r="J55" s="75" t="s">
+      <c r="J55" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="75"/>
-      <c r="L55" s="75"/>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
       <c r="R55" s="10"/>
     </row>
     <row r="56" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7581,13 +7615,2725 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.25">
       <c r="H59" s="43"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="55"/>
+      <c r="J59" s="91"/>
+      <c r="K59" s="91"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.25">
       <c r="H61" s="43"/>
-      <c r="J61" s="55"/>
-      <c r="K61" s="55"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="I2:R9"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:R13"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="H24:L24"/>
+    <mergeCell ref="N24:R24"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="H35:L35"/>
+    <mergeCell ref="N35:R35"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="H46:R46"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="P50:R50"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="M54:O54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C14:C22">
+    <cfRule type="expression" dxfId="84" priority="40">
+      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&gt;$E14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="39">
+      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&lt;$E14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:C33">
+    <cfRule type="expression" dxfId="82" priority="35">
+      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$D25&lt;$E25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="36">
+      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$D25&gt;$E25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36:C44">
+    <cfRule type="expression" dxfId="80" priority="19">
+      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$D36&lt;$E36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="20">
+      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$D36&gt;$E36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47:C55">
+    <cfRule type="expression" dxfId="78" priority="15">
+      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$D47&lt;$E47)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="16">
+      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$D47&gt;$E47)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F22">
+    <cfRule type="expression" dxfId="76" priority="37">
+      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$E14&lt;$D14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="38">
+      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$E14&gt;$D14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:F33">
+    <cfRule type="expression" dxfId="74" priority="33">
+      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$E25&lt;$D25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="34">
+      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$E25&gt;$D25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36:F44">
+    <cfRule type="expression" dxfId="72" priority="17">
+      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$E36&lt;$D36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="18">
+      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$E36&gt;$D36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47:F55">
+    <cfRule type="expression" dxfId="70" priority="13">
+      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$E47&lt;$D47)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="14">
+      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$E47&gt;$D47)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14:I22">
+    <cfRule type="expression" dxfId="68" priority="32">
+      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="31">
+      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25:I33">
+    <cfRule type="expression" dxfId="66" priority="28">
+      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="27">
+      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I36:I44">
+    <cfRule type="expression" dxfId="64" priority="24">
+      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="23">
+      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&lt;$K36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14:L22">
+    <cfRule type="expression" dxfId="62" priority="30">
+      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="29">
+      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L25:L33">
+    <cfRule type="expression" dxfId="60" priority="26">
+      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="25">
+      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L36:L44">
+    <cfRule type="expression" dxfId="58" priority="21">
+      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="22">
+      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&lt;$K36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O14:O22">
+    <cfRule type="expression" dxfId="56" priority="12">
+      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="11">
+      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O25:O33">
+    <cfRule type="expression" dxfId="54" priority="8">
+      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="7">
+      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O36:O44">
+    <cfRule type="expression" dxfId="52" priority="4">
+      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="3">
+      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R14:R22">
+    <cfRule type="expression" dxfId="50" priority="10">
+      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="9">
+      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R25:R33">
+    <cfRule type="expression" dxfId="48" priority="6">
+      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="5">
+      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R36:R44">
+    <cfRule type="expression" dxfId="46" priority="2">
+      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="1">
+      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I49:I52 L49:L54 O50:O51" xr:uid="{2AC35715-5126-4C8B-836F-977311BB5FC7}">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O52:O53 R51:R52" xr:uid="{83DD0C4F-2D9C-477E-B1A0-35299695F693}">
+      <formula1>"0,1,2,3,4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:E22 D25:E33 J14:K22 J25:K33 J36:K44 D36:E44 D47:E55 P14:Q22 P25:Q33 P36:Q44" xr:uid="{84190180-2645-4B02-8CB0-15E965C4AB48}">
+      <formula1>"0,1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C22 F14:F22 C25:C33 F25:F33 I14:I22 L14:L22 I25:I33 L25:L33 I36:I44 L36:L44 C36:C44 F36:F44 C47:C55 F47:F55 O14:O22 R14:R22 O25:O33 R25:R33 O36:O44 R36:R44" xr:uid="{354B0928-FEA4-44A4-91F9-500AA7B5A44B}">
+      <formula1>$B$3:$B$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88F88CA8-152B-4E13-A79E-101E8F3D79F7}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BN61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="19.5703125" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="7.85546875" customWidth="1"/>
+    <col min="58" max="58" width="11" customWidth="1"/>
+    <col min="59" max="61" width="7.85546875" customWidth="1"/>
+    <col min="62" max="65" width="9.140625" customWidth="1"/>
+    <col min="66" max="66" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:66" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="85"/>
+      <c r="I1" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="8"/>
+      <c r="BF1" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="BG1" s="25">
+        <f>SUMPRODUCT(($C$14:$C$22=$BF1)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF1)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF1)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF1)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF1)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF1)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF1)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF1)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF1)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF1)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF1)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF1)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF1)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF1)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF1)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF1)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF1)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF1)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
+        <v>1</v>
+      </c>
+      <c r="BH1" s="25">
+        <f>SUMPRODUCT(($C$14:$C$22=$BF1)*($D$14:$D$22-$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF1)*($E$14:$E$22-$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF1)*($J$14:$J$22-$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF1)*($K$14:$K$22-$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF1)*($P$14:$P$22-$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF1)*($Q$14:$Q$22-$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF1)*($D$25:$D$33-$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF1)*($E$25:$E$33-$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF1)*($J$25:$J$33-$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF1)*($K$25:$K$33-$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF1)*($P$25:$P$33-$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF1)*($Q$25:$Q$33-$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF1)*($D$36:$D$44-$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF1)*($E$36:$E$44-$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF1)*($J$36:$J$44-$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF1)*($K$36:$K$44-$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF1)*($P$36:$P$44-$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF1)*($Q$36:$Q$44-$P$36:$P$44))+SUMPRODUCT(($C$47:$C$55=$BF1)*($D$47:$D$55-$E$47:$E$55))+SUMPRODUCT(($F$47:$F$55=$BF1)*($E$47:$E$55-$D$47:$D$55))</f>
+        <v>-16</v>
+      </c>
+      <c r="BI1" s="25">
+        <f>IF(AND($BG$1=BG1,$BH$1=BH1,$BF$1&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$1,$BG$12:$BN$12,0)),0)+IF(AND($BG$2=BG1,$BH$2=BH1,$BF$2&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$2,$BG$12:$BN$12,0)),0)+IF(AND($BG$3=BG1,$BH$3=BH1,$BF$3&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$3,$BG$12:$BN$12,0)),0)+IF(AND($BG$4=BG1,$BH$4=BH1,$BF$4&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$4,$BG$12:$BN$12,0)),0)+IF(AND($BG$5=BG1,$BH$5=BH1,$BF$5&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$5,$BG$12:$BN$12,0)),0)+IF(AND($BG$6=BG1,$BH$6=BH1,$BF$6&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$6,$BG$12:$BN$12,0)),0)+IF(AND($BG$7=BG1,$BH$7=BH1,$BF$7&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$7,$BG$12:$BN$12,0)),0)+IF(AND($BG$8=BG1,$BH$8=BH1,$BF$8&lt;&gt;BF1),INDEX($BG$13:$BN$20,MATCH(BF1,$BF$13:$BF$20,0),MATCH($BF$8,$BG$12:$BN$12,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ1" s="25">
+        <f>IF(AND($BG$1=BG1,$BH$1=BH1,$BF$1&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$1,$BG$24:$BN$24,0)),0)+IF(AND($BG$2=BG1,$BH$2=BH1,$BF$2&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$2,$BG$24:$BN$24,0)),0)+IF(AND($BG$3=BG1,$BH$3=BH1,$BF$3&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$3,$BG$24:$BN$24,0)),0)+IF(AND($BG$4=BG1,$BH$4=BH1,$BF$4&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$4,$BG$24:$BN$24,0)),0)+IF(AND($BG$5=BG1,$BH$5=BH1,$BF$5&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$5,$BG$24:$BN$24,0)),0)+IF(AND($BG$6=BG1,$BH$6=BH1,$BF$6&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$6,$BG$24:$BN$24,0)),0)+IF(AND($BG$7=BG1,$BH$7=BH1,$BF$7&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$7,$BG$24:$BN$24,0)),0)+IF(AND($BG$8=BG1,$BH$8=BH1,$BF$8&lt;&gt;BF1),INDEX($BG$25:$BN$32,MATCH(BF1,$BF$25:$BF$32,0),MATCH($BF$8,$BG$24:$BN$24,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK1" s="56">
+        <f>1+SUMPRODUCT(--($BG$1:$BG$8&gt;BG1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8&gt;BH1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8=BH1),--($BI$1:$BI$8&gt;BI1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8=BH1),--($BI$1:$BI$8=BI1),--($BJ$1:$BJ$8&gt;BJ1))+SUMPRODUCT(--($BG$1:$BG$8=BG1),--($BH$1:$BH$8=BH1),--($BI$1:$BI$8=BI1),--($BJ$1:$BJ$8=BJ1),--($BF$1:$BF$8&lt;BF1))</f>
+        <v>8</v>
+      </c>
+      <c r="BL1" s="25"/>
+    </row>
+    <row r="2" spans="1:66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="95" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="97"/>
+      <c r="BF2" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="BG2" s="25">
+        <f t="shared" ref="BG2:BG8" si="0">SUMPRODUCT(($C$14:$C$22=$BF2)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF2)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF2)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF2)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF2)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF2)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF2)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF2)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF2)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF2)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF2)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF2)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF2)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF2)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF2)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF2)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF2)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF2)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
+        <v>5</v>
+      </c>
+      <c r="BH2" s="25">
+        <f t="shared" ref="BH2:BH8" si="1">SUMPRODUCT(($C$14:$C$22=$BF2)*($D$14:$D$22-$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF2)*($E$14:$E$22-$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF2)*($J$14:$J$22-$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF2)*($K$14:$K$22-$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF2)*($P$14:$P$22-$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF2)*($Q$14:$Q$22-$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF2)*($D$25:$D$33-$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF2)*($E$25:$E$33-$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF2)*($J$25:$J$33-$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF2)*($K$25:$K$33-$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF2)*($P$25:$P$33-$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF2)*($Q$25:$Q$33-$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF2)*($D$36:$D$44-$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF2)*($E$36:$E$44-$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF2)*($J$36:$J$44-$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF2)*($K$36:$K$44-$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF2)*($P$36:$P$44-$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF2)*($Q$36:$Q$44-$P$36:$P$44))+SUMPRODUCT(($C$47:$C$55=$BF2)*($D$47:$D$55-$E$47:$E$55))+SUMPRODUCT(($F$47:$F$55=$BF2)*($E$47:$E$55-$D$47:$D$55))</f>
+        <v>-1</v>
+      </c>
+      <c r="BI2" s="25">
+        <f t="shared" ref="BI2:BI8" si="2">IF(AND($BG$1=BG2,$BH$1=BH2,$BF$1&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$1,$BG$12:$BN$12,0)),0)+IF(AND($BG$2=BG2,$BH$2=BH2,$BF$2&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$2,$BG$12:$BN$12,0)),0)+IF(AND($BG$3=BG2,$BH$3=BH2,$BF$3&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$3,$BG$12:$BN$12,0)),0)+IF(AND($BG$4=BG2,$BH$4=BH2,$BF$4&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$4,$BG$12:$BN$12,0)),0)+IF(AND($BG$5=BG2,$BH$5=BH2,$BF$5&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$5,$BG$12:$BN$12,0)),0)+IF(AND($BG$6=BG2,$BH$6=BH2,$BF$6&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$6,$BG$12:$BN$12,0)),0)+IF(AND($BG$7=BG2,$BH$7=BH2,$BF$7&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$7,$BG$12:$BN$12,0)),0)+IF(AND($BG$8=BG2,$BH$8=BH2,$BF$8&lt;&gt;BF2),INDEX($BG$13:$BN$20,MATCH(BF2,$BF$13:$BF$20,0),MATCH($BF$8,$BG$12:$BN$12,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="25">
+        <f t="shared" ref="BJ2:BJ8" si="3">IF(AND($BG$1=BG2,$BH$1=BH2,$BF$1&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$1,$BG$24:$BN$24,0)),0)+IF(AND($BG$2=BG2,$BH$2=BH2,$BF$2&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$2,$BG$24:$BN$24,0)),0)+IF(AND($BG$3=BG2,$BH$3=BH2,$BF$3&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$3,$BG$24:$BN$24,0)),0)+IF(AND($BG$4=BG2,$BH$4=BH2,$BF$4&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$4,$BG$24:$BN$24,0)),0)+IF(AND($BG$5=BG2,$BH$5=BH2,$BF$5&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$5,$BG$24:$BN$24,0)),0)+IF(AND($BG$6=BG2,$BH$6=BH2,$BF$6&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$6,$BG$24:$BN$24,0)),0)+IF(AND($BG$7=BG2,$BH$7=BH2,$BF$7&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$7,$BG$24:$BN$24,0)),0)+IF(AND($BG$8=BG2,$BH$8=BH2,$BF$8&lt;&gt;BF2),INDEX($BG$25:$BN$32,MATCH(BF2,$BF$25:$BF$32,0),MATCH($BF$8,$BG$24:$BN$24,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK2" s="56">
+        <f t="shared" ref="BK2:BK8" si="4">1+SUMPRODUCT(--($BG$1:$BG$8&gt;BG2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8&gt;BH2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8=BH2),--($BI$1:$BI$8&gt;BI2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8=BH2),--($BI$1:$BI$8=BI2),--($BJ$1:$BJ$8&gt;BJ2))+SUMPRODUCT(--($BG$1:$BG$8=BG2),--($BH$1:$BH$8=BH2),--($BI$1:$BI$8=BI2),--($BJ$1:$BJ$8=BJ2),--($BF$1:$BF$8&lt;BF2))</f>
+        <v>5</v>
+      </c>
+      <c r="BL2" s="25"/>
+    </row>
+    <row r="3" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="27">
+        <v>1</v>
+      </c>
+      <c r="B3" s="28" t="str">
+        <f>INDEX($BF$1:$BF$8,MATCH(ROW()-2,$BK$1:$BK$8,0))</f>
+        <v>SRG</v>
+      </c>
+      <c r="C3" s="29">
+        <f t="shared" ref="C3:C10" si="5">SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
+        <v>9</v>
+      </c>
+      <c r="D3" s="29">
+        <f t="shared" ref="D3:D10" si="6">SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
+        <v>2</v>
+      </c>
+      <c r="E3" s="29">
+        <f>SUMIF($C$14:$C$22,$B3,$D$14:$D$22)+SUMIF($F$14:$F$22,$B3,$E$14:$E$22)+SUMIF($I$14:$I$22,$B3,$J$14:$J$22)+SUMIF($L$14:$L$22,$B3,$K$14:$K$22)+SUMIF($O$14:$O$22,$B3,$P$14:$P$22)+SUMIF($R$14:$R$22,$B3,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B3,$D$25:$D$33)+SUMIF($F$25:$F$33,$B3,$E$25:$E$33)+SUMIF($I$25:$I$33,$B3,$J$25:$J$33)+SUMIF($L$25:$L$33,$B3,$K$25:$K$33)+SUMIF($O$25:$O$33,$B3,$P$25:$P$33)+SUMIF($R$25:$R$33,$B3,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B3,$D$36:$D$44)+SUMIF($F$36:$F$44,$B3,$E$36:$E$44)+SUMIF($I$36:$I$44,$B3,$J$36:$J$44)+SUMIF($L$36:$L$44,$B3,$K$36:$K$44)+SUMIF($O$36:$O$44,$B3,$P$36:$P$44)+SUMIF($R$36:$R$44,$B3,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
+        <v>20</v>
+      </c>
+      <c r="F3" s="29">
+        <f t="shared" ref="F3:F10" si="7">SUMIF($C$14:$C$22,$B3,$E$14:$E$22)+SUMIF($F$14:$F$22,$B3,$D$14:$D$22)+SUMIF($I$14:$I$22,$B3,$K$14:$K$22)+SUMIF($L$14:$L$22,$B3,$J$14:$J$22)+SUMIF($O$14:$O$22,$B3,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B3,$P$14:$P$22)+SUMIF($C$25:$C$33,$B3,$E$25:$E$33)+SUMIF($F$25:$F$33,$B3,$D$25:$D$33)+SUMIF($I$25:$I$33,$B3,$K$25:$K$33)+SUMIF($L$25:$L$33,$B3,$J$25:$J$33)+SUMIF($O$25:$O$33,$B3,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B3,$P$25:$P$33)+SUMIF($C$36:$C$44,$B3,$E$36:$E$44)+SUMIF($F$36:$F$44,$B3,$D$36:$D$44)+SUMIF($I$36:$I$44,$B3,$K$36:$K$44)+SUMIF($L$36:$L$44,$B3,$J$36:$J$44)+SUMIF($O$36:$O$44,$B3,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B3,$P$36:$P$44)+SUMIF($C$47:$C$55,$B3,$E$47:$E$55)+SUMIF($F$47:$F$55,$B3,$D$47:$D$55)</f>
+        <v>6</v>
+      </c>
+      <c r="G3" s="30">
+        <f t="shared" ref="G3:G10" si="8">E3-F3</f>
+        <v>14</v>
+      </c>
+      <c r="I3" s="95"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="97"/>
+      <c r="BF3" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="BG3" s="25">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="BH3" s="25">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="BI3" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BK3" s="56">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="BL3" s="25"/>
+    </row>
+    <row r="4" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="27">
+        <v>2</v>
+      </c>
+      <c r="B4" s="28" t="str">
+        <f t="shared" ref="B4:B10" si="9">INDEX($BF$1:$BF$8,MATCH(ROW()-2,$BK$1:$BK$8,0))</f>
+        <v>T. REY</v>
+      </c>
+      <c r="C4" s="29">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="29">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="E4" s="29">
+        <f>SUMIF($C$14:$C$22,$B4,$D$14:$D$22)+SUMIF($F$14:$F$22,$B4,$E$14:$E$22)+SUMIF($I$14:$I$22,$B4,$J$14:$J$22)+SUMIF($L$14:$L$22,$B4,$K$14:$K$22)+SUMIF($O$14:$O$22,$B4,$P$14:$P$22)+SUMIF($R$14:$R$22,$B4,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B4,$D$25:$D$33)+SUMIF($F$25:$F$33,$B4,$E$25:$E$33)+SUMIF($I$25:$I$33,$B4,$J$25:$J$33)+SUMIF($L$25:$L$33,$B4,$K$25:$K$33)+SUMIF($O$25:$O$33,$B4,$P$25:$P$33)+SUMIF($R$25:$R$33,$B4,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B4,$D$36:$D$44)+SUMIF($F$36:$F$44,$B4,$E$36:$E$44)+SUMIF($I$36:$I$44,$B4,$J$36:$J$44)+SUMIF($L$36:$L$44,$B4,$K$36:$K$44)+SUMIF($O$36:$O$44,$B4,$P$36:$P$44)+SUMIF($R$36:$R$44,$B4,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B4,$D$47:$D$55)+SUMIF($F$47:$F$55,$B4,$E$47:$E$55)</f>
+        <v>17</v>
+      </c>
+      <c r="F4" s="29">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="G4" s="30">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="I4" s="95"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="97"/>
+      <c r="BF4" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG4" s="25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="BH4" s="25">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+      <c r="BI4" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BK4" s="56">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BL4" s="25"/>
+    </row>
+    <row r="5" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="57">
+        <v>3</v>
+      </c>
+      <c r="B5" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>T. VAMOS</v>
+      </c>
+      <c r="C5" s="59">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="D5" s="59">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="59">
+        <f>SUMIF($C$14:$C$22,$B5,$D$14:$D$22)+SUMIF($F$14:$F$22,$B5,$E$14:$E$22)+SUMIF($I$14:$I$22,$B5,$J$14:$J$22)+SUMIF($L$14:$L$22,$B5,$K$14:$K$22)+SUMIF($O$14:$O$22,$B5,$P$14:$P$22)+SUMIF($R$14:$R$22,$B5,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B5,$D$25:$D$33)+SUMIF($F$25:$F$33,$B5,$E$25:$E$33)+SUMIF($I$25:$I$33,$B5,$J$25:$J$33)+SUMIF($L$25:$L$33,$B5,$K$25:$K$33)+SUMIF($O$25:$O$33,$B5,$P$25:$P$33)+SUMIF($R$25:$R$33,$B5,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B5,$D$36:$D$44)+SUMIF($F$36:$F$44,$B5,$E$36:$E$44)+SUMIF($I$36:$I$44,$B5,$J$36:$J$44)+SUMIF($L$36:$L$44,$B5,$K$36:$K$44)+SUMIF($O$36:$O$44,$B5,$P$36:$P$44)+SUMIF($R$36:$R$44,$B5,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
+        <v>15</v>
+      </c>
+      <c r="F5" s="59">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="G5" s="60">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="I5" s="95"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="97"/>
+      <c r="BF5" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="BG5" s="25">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="BH5" s="25">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="BI5" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BK5" s="56">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="BL5" s="25"/>
+    </row>
+    <row r="6" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="53">
+        <v>4</v>
+      </c>
+      <c r="B6" s="46" t="str">
+        <f t="shared" si="9"/>
+        <v>IG</v>
+      </c>
+      <c r="C6" s="51">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="D6" s="51">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="51">
+        <f>SUMIF($C$14:$C$22,$B6,$D$14:$D$22)+SUMIF($F$14:$F$22,$B6,$E$14:$E$22)+SUMIF($I$14:$I$22,$B6,$J$14:$J$22)+SUMIF($L$14:$L$22,$B6,$K$14:$K$22)+SUMIF($O$14:$O$22,$B6,$P$14:$P$22)+SUMIF($R$14:$R$22,$B6,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B6,$D$25:$D$33)+SUMIF($F$25:$F$33,$B6,$E$25:$E$33)+SUMIF($I$25:$I$33,$B6,$J$25:$J$33)+SUMIF($L$25:$L$33,$B6,$K$25:$K$33)+SUMIF($O$25:$O$33,$B6,$P$25:$P$33)+SUMIF($R$25:$R$33,$B6,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B6,$D$36:$D$44)+SUMIF($F$36:$F$44,$B6,$E$36:$E$44)+SUMIF($I$36:$I$44,$B6,$J$36:$J$44)+SUMIF($L$36:$L$44,$B6,$K$36:$K$44)+SUMIF($O$36:$O$44,$B6,$P$36:$P$44)+SUMIF($R$36:$R$44,$B6,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B4,$D$47:$D$55)+SUMIF($F$47:$F$55,$B4,$E$47:$E$55)</f>
+        <v>13</v>
+      </c>
+      <c r="F6" s="51">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
+      <c r="BF6" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="BG6" s="25">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="BH6" s="25">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="BI6" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BK6" s="56">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="BL6" s="25"/>
+    </row>
+    <row r="7" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="53">
+        <v>5</v>
+      </c>
+      <c r="B7" s="46" t="str">
+        <f t="shared" si="9"/>
+        <v>BTR MY</v>
+      </c>
+      <c r="C7" s="51">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="D7" s="51">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="E7" s="51">
+        <f>SUMIF($C$14:$C$22,$B7,$D$14:$D$22)+SUMIF($F$14:$F$22,$B7,$E$14:$E$22)+SUMIF($I$14:$I$22,$B7,$J$14:$J$22)+SUMIF($L$14:$L$22,$B7,$K$14:$K$22)+SUMIF($O$14:$O$22,$B7,$P$14:$P$22)+SUMIF($R$14:$R$22,$B7,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B7,$D$25:$D$33)+SUMIF($F$25:$F$33,$B7,$E$25:$E$33)+SUMIF($I$25:$I$33,$B7,$J$25:$J$33)+SUMIF($L$25:$L$33,$B7,$K$25:$K$33)+SUMIF($O$25:$O$33,$B7,$P$25:$P$33)+SUMIF($R$25:$R$33,$B7,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B7,$D$36:$D$44)+SUMIF($F$36:$F$44,$B7,$E$36:$E$44)+SUMIF($I$36:$I$44,$B7,$J$36:$J$44)+SUMIF($L$36:$L$44,$B7,$K$36:$K$44)+SUMIF($O$36:$O$44,$B7,$P$36:$P$44)+SUMIF($R$36:$R$44,$B7,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B5,$D$47:$D$55)+SUMIF($F$47:$F$55,$B5,$E$47:$E$55)</f>
+        <v>14</v>
+      </c>
+      <c r="F7" s="51">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="8"/>
+        <v>-1</v>
+      </c>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="97"/>
+      <c r="BF7" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="BG7" s="25">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="BH7" s="25">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="BI7" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BK7" s="56">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BL7" s="25"/>
+    </row>
+    <row r="8" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="57">
+        <v>6</v>
+      </c>
+      <c r="B8" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>T. FLASH</v>
+      </c>
+      <c r="C8" s="59">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="D8" s="59">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="E8" s="59">
+        <f>SUMIF($C$14:$C$22,$B8,$D$14:$D$22)+SUMIF($F$14:$F$22,$B8,$E$14:$E$22)+SUMIF($I$14:$I$22,$B8,$J$14:$J$22)+SUMIF($L$14:$L$22,$B8,$K$14:$K$22)+SUMIF($O$14:$O$22,$B8,$P$14:$P$22)+SUMIF($R$14:$R$22,$B8,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B8,$D$25:$D$33)+SUMIF($F$25:$F$33,$B8,$E$25:$E$33)+SUMIF($I$25:$I$33,$B8,$J$25:$J$33)+SUMIF($L$25:$L$33,$B8,$K$25:$K$33)+SUMIF($O$25:$O$33,$B8,$P$25:$P$33)+SUMIF($R$25:$R$33,$B8,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B8,$D$36:$D$44)+SUMIF($F$36:$F$44,$B8,$E$36:$E$44)+SUMIF($I$36:$I$44,$B8,$J$36:$J$44)+SUMIF($L$36:$L$44,$B8,$K$36:$K$44)+SUMIF($O$36:$O$44,$B8,$P$36:$P$44)+SUMIF($R$36:$R$44,$B8,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B6,$D$47:$D$55)+SUMIF($F$47:$F$55,$B6,$E$47:$E$55)</f>
+        <v>11</v>
+      </c>
+      <c r="F8" s="59">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="G8" s="60">
+        <f t="shared" si="8"/>
+        <v>-1</v>
+      </c>
+      <c r="I8" s="95"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="97"/>
+      <c r="BF8" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="BG8" s="25">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="BH8" s="25">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="BI8" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BK8" s="56">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="BL8" s="25"/>
+    </row>
+    <row r="9" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="61">
+        <v>7</v>
+      </c>
+      <c r="B9" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>RRQ T</v>
+      </c>
+      <c r="C9" s="39">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="D9" s="39">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="E9" s="39">
+        <f>SUMIF($C$14:$C$22,$B9,$D$14:$D$22)+SUMIF($F$14:$F$22,$B9,$E$14:$E$22)+SUMIF($I$14:$I$22,$B9,$J$14:$J$22)+SUMIF($L$14:$L$22,$B9,$K$14:$K$22)+SUMIF($O$14:$O$22,$B9,$P$14:$P$22)+SUMIF($R$14:$R$22,$B9,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B9,$D$25:$D$33)+SUMIF($F$25:$F$33,$B9,$E$25:$E$33)+SUMIF($I$25:$I$33,$B9,$J$25:$J$33)+SUMIF($L$25:$L$33,$B9,$K$25:$K$33)+SUMIF($O$25:$O$33,$B9,$P$25:$P$33)+SUMIF($R$25:$R$33,$B9,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B9,$D$36:$D$44)+SUMIF($F$36:$F$44,$B9,$E$36:$E$44)+SUMIF($I$36:$I$44,$B9,$J$36:$J$44)+SUMIF($L$36:$L$44,$B9,$K$36:$K$44)+SUMIF($O$36:$O$44,$B9,$P$36:$P$44)+SUMIF($R$36:$R$44,$B9,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
+        <v>9</v>
+      </c>
+      <c r="F9" s="39">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="G9" s="62">
+        <f t="shared" si="8"/>
+        <v>-10</v>
+      </c>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="97"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="25"/>
+      <c r="BI9" s="25"/>
+      <c r="BJ9" s="25"/>
+      <c r="BL9" s="25"/>
+    </row>
+    <row r="10" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="61">
+        <v>8</v>
+      </c>
+      <c r="B10" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>AC</v>
+      </c>
+      <c r="C10" s="39">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D10" s="39">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="E10" s="39">
+        <f>SUMIF($C$14:$C$22,$B10,$D$14:$D$22)+SUMIF($F$14:$F$22,$B10,$E$14:$E$22)+SUMIF($I$14:$I$22,$B10,$J$14:$J$22)+SUMIF($L$14:$L$22,$B10,$K$14:$K$22)+SUMIF($O$14:$O$22,$B10,$P$14:$P$22)+SUMIF($R$14:$R$22,$B10,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B10,$D$25:$D$33)+SUMIF($F$25:$F$33,$B10,$E$25:$E$33)+SUMIF($I$25:$I$33,$B10,$J$25:$J$33)+SUMIF($L$25:$L$33,$B10,$K$25:$K$33)+SUMIF($O$25:$O$33,$B10,$P$25:$P$33)+SUMIF($R$25:$R$33,$B10,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B10,$D$36:$D$44)+SUMIF($F$36:$F$44,$B10,$E$36:$E$44)+SUMIF($I$36:$I$44,$B10,$J$36:$J$44)+SUMIF($L$36:$L$44,$B10,$K$36:$K$44)+SUMIF($O$36:$O$44,$B10,$P$36:$P$44)+SUMIF($R$36:$R$44,$B10,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B4,$D$47:$D$55)+SUMIF($F$47:$F$55,$B4,$E$47:$E$55)</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="39">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="G10" s="62">
+        <f t="shared" si="8"/>
+        <v>-16</v>
+      </c>
+      <c r="I10" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="100"/>
+    </row>
+    <row r="11" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="65"/>
+    </row>
+    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BG12" t="str">
+        <f>BF13</f>
+        <v>AC</v>
+      </c>
+      <c r="BH12" t="str">
+        <f>BF14</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="BI12" t="str">
+        <f>BF15</f>
+        <v>IG</v>
+      </c>
+      <c r="BJ12" t="str">
+        <f>BF16</f>
+        <v>RRQ T</v>
+      </c>
+      <c r="BK12" t="str">
+        <f>BF17</f>
+        <v>SRG</v>
+      </c>
+      <c r="BL12" t="str">
+        <f>BF18</f>
+        <v>T. FLASH</v>
+      </c>
+      <c r="BM12" t="str">
+        <f>BF19</f>
+        <v>T. REY</v>
+      </c>
+      <c r="BN12" t="str">
+        <f>BF20</f>
+        <v>T. VAMOS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="88"/>
+      <c r="H13" s="86" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="88"/>
+      <c r="N13" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
+      <c r="BF13" s="25" t="str">
+        <f>BF1</f>
+        <v>AC</v>
+      </c>
+      <c r="BG13">
+        <f>SUMPRODUCT(($C$14:$C$22=$BF13)*($F$14:$F$22=BG$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF13)*($C$14:$C$22=BG$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF13)*($L$14:$L$22=BG$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF13)*($I$14:$I$22=BG$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF13)*($R$14:$R$22=BG$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF13)*($O$14:$O$22=BG$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF13)*($F$25:$F$33=BG$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF13)*($C$25:$C$33=BG$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF13)*($L$25:$L$33=BG$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF13)*($I$25:$I$33=BG$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF13)*($R$25:$R$33=BG$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF13)*($O$25:$O$33=BG$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF13)*($F$37:$F$45=BG$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF13)*($C$37:$C$45=BG$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF13)*($L$37:$L$45=BG$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF13)*($I$37:$I$45=BG$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF13)*($R$37:$R$45=BG$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF13)*($O$37:$O$45=BG$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <f t="shared" ref="BH13:BN20" si="10">SUMPRODUCT(($C$14:$C$22=$BF13)*($F$14:$F$22=BH$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF13)*($C$14:$C$22=BH$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF13)*($L$14:$L$22=BH$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF13)*($I$14:$I$22=BH$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF13)*($R$14:$R$22=BH$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF13)*($O$14:$O$22=BH$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF13)*($F$25:$F$33=BH$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF13)*($C$25:$C$33=BH$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF13)*($L$25:$L$33=BH$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF13)*($I$25:$I$33=BH$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF13)*($R$25:$R$33=BH$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF13)*($O$25:$O$33=BH$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF13)*($F$37:$F$45=BH$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF13)*($C$37:$C$45=BH$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF13)*($L$37:$L$45=BH$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF13)*($I$37:$I$45=BH$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF13)*($R$37:$R$45=BH$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF13)*($O$37:$O$45=BH$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BK13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="23">
+        <v>1</v>
+      </c>
+      <c r="E14" s="23">
+        <v>2</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="23">
+        <v>2</v>
+      </c>
+      <c r="K14" s="23">
+        <v>1</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="P14" s="23">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>2</v>
+      </c>
+      <c r="R14" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF14" s="25" t="str">
+        <f t="shared" ref="BF14:BF20" si="11">BF2</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="BG14">
+        <f t="shared" ref="BG14:BG20" si="12">SUMPRODUCT(($C$14:$C$22=$BF14)*($F$14:$F$22=BG$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF14)*($C$14:$C$22=BG$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF14)*($L$14:$L$22=BG$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF14)*($I$14:$I$22=BG$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF14)*($R$14:$R$22=BG$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF14)*($O$14:$O$22=BG$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF14)*($F$25:$F$33=BG$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF14)*($C$25:$C$33=BG$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF14)*($L$25:$L$33=BG$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF14)*($I$25:$I$33=BG$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF14)*($R$25:$R$33=BG$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF14)*($O$25:$O$33=BG$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF14)*($F$37:$F$45=BG$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF14)*($C$37:$C$45=BG$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF14)*($L$37:$L$45=BG$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF14)*($I$37:$I$45=BG$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF14)*($R$37:$R$45=BG$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF14)*($O$37:$O$45=BG$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
+        <v>2</v>
+      </c>
+      <c r="BH14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BJ14">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BK14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BM14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P15" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>1</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="BF15" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>IG</v>
+      </c>
+      <c r="BG15">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="BH15">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BI15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BK15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BN15">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="6"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="6"/>
+      <c r="BF16" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>RRQ T</v>
+      </c>
+      <c r="BG16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BL16">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BM16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="23">
+        <v>1</v>
+      </c>
+      <c r="E17" s="23">
+        <v>2</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="23">
+        <v>1</v>
+      </c>
+      <c r="K17" s="23">
+        <v>2</v>
+      </c>
+      <c r="L17" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="P17" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>2</v>
+      </c>
+      <c r="R17" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF17" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>SRG</v>
+      </c>
+      <c r="BG17">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="BH17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BI17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BJ17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BK17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BM17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BN17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>2</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>2</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF18" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>T. FLASH</v>
+      </c>
+      <c r="BG18">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="BH18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BJ18">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BK18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="5">
+        <v>2</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N19" s="4"/>
+      <c r="O19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P19" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="BF19" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>T. REY</v>
+      </c>
+      <c r="BG19">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="BH19">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BI19">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BJ19">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BK19">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BL19">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BM19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="23">
+        <v>2</v>
+      </c>
+      <c r="E20" s="23">
+        <v>0</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="23">
+        <v>2</v>
+      </c>
+      <c r="K20" s="23">
+        <v>0</v>
+      </c>
+      <c r="L20" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="P20" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>2</v>
+      </c>
+      <c r="R20" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="BF20" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>T. VAMOS</v>
+      </c>
+      <c r="BG20">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="BH20">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BI20">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BK20">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BM20">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BN20">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>2</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BF21" s="25"/>
+    </row>
+    <row r="22" spans="2:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="6"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="6"/>
+    </row>
+    <row r="24" spans="2:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="88"/>
+      <c r="H24" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="88"/>
+      <c r="N24" s="86" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="87"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
+      <c r="BG24" t="str">
+        <f>BF25</f>
+        <v>AC</v>
+      </c>
+      <c r="BH24" t="str">
+        <f>BF26</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="BI24" t="str">
+        <f>BF27</f>
+        <v>IG</v>
+      </c>
+      <c r="BJ24" t="str">
+        <f>BF28</f>
+        <v>RRQ T</v>
+      </c>
+      <c r="BK24" t="str">
+        <f>BF29</f>
+        <v>SRG</v>
+      </c>
+      <c r="BL24" t="str">
+        <f>BF30</f>
+        <v>T. FLASH</v>
+      </c>
+      <c r="BM24" t="str">
+        <f>BF31</f>
+        <v>T. REY</v>
+      </c>
+      <c r="BN24" t="str">
+        <f>BF32</f>
+        <v>T. VAMOS</v>
+      </c>
+    </row>
+    <row r="25" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="23">
+        <v>0</v>
+      </c>
+      <c r="E25" s="23">
+        <v>2</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="23">
+        <v>2</v>
+      </c>
+      <c r="K25" s="23">
+        <v>0</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="N25" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="P25" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="BF25" s="25" t="str">
+        <f>BF13</f>
+        <v>AC</v>
+      </c>
+      <c r="BG25">
+        <f>SUMPRODUCT(($C$14:$C$22=$BF25)*($F$14:$F$22=BG$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF25)*($C$14:$C$22=BG$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF25)*($L$14:$L$22=BG$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF25)*($I$14:$I$22=BG$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF25)*($R$14:$R$22=BG$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF25)*($O$14:$O$22=BG$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF25)*($F$25:$F$33=BG$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF25)*($C$25:$C$33=BG$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF25)*($L$25:$L$33=BG$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF25)*($I$25:$I$33=BG$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF25)*($R$25:$R$33=BG$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF25)*($O$25:$O$33=BG$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF25)*($F$36:$F$44=BG$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF25)*($C$36:$C$44=BG$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF25)*($L$36:$L$44=BG$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF25)*($I$36:$I$44=BG$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF25)*($R$36:$R$44=BG$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF25)*($O$36:$O$44=BG$24)*$Q$36:$Q$44)</f>
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <f t="shared" ref="BH25:BN32" si="13">SUMPRODUCT(($C$14:$C$22=$BF25)*($F$14:$F$22=BH$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF25)*($C$14:$C$22=BH$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF25)*($L$14:$L$22=BH$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF25)*($I$14:$I$22=BH$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF25)*($R$14:$R$22=BH$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF25)*($O$14:$O$22=BH$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF25)*($F$25:$F$33=BH$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF25)*($C$25:$C$33=BH$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF25)*($L$25:$L$33=BH$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF25)*($I$25:$I$33=BH$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF25)*($R$25:$R$33=BH$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF25)*($O$25:$O$33=BH$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF25)*($F$36:$F$44=BH$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF25)*($C$36:$C$44=BH$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF25)*($L$36:$L$44=BH$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF25)*($I$36:$I$44=BH$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF25)*($R$36:$R$44=BH$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF25)*($O$36:$O$44=BH$24)*$Q$36:$Q$44)</f>
+        <v>1</v>
+      </c>
+      <c r="BI25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BK25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="C26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>2</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF26" s="25" t="str">
+        <f t="shared" ref="BF26:BF32" si="14">BF14</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="BG26">
+        <f t="shared" ref="BG26:BG32" si="15">SUMPRODUCT(($C$14:$C$22=$BF26)*($F$14:$F$22=BG$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF26)*($C$14:$C$22=BG$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF26)*($L$14:$L$22=BG$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF26)*($I$14:$I$22=BG$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF26)*($R$14:$R$22=BG$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF26)*($O$14:$O$22=BG$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF26)*($F$25:$F$33=BG$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF26)*($C$25:$C$33=BG$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF26)*($L$25:$L$33=BG$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF26)*($I$25:$I$33=BG$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF26)*($R$25:$R$33=BG$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF26)*($O$25:$O$33=BG$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF26)*($F$36:$F$44=BG$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF26)*($C$36:$C$44=BG$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF26)*($L$36:$L$44=BG$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF26)*($I$36:$I$44=BG$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF26)*($R$36:$R$44=BG$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF26)*($O$36:$O$44=BG$24)*$Q$36:$Q$44)</f>
+        <v>4</v>
+      </c>
+      <c r="BH26">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="BJ26">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BK26">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BL26">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BM26">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BN26">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="6"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="6"/>
+      <c r="BF27" s="25" t="str">
+        <f t="shared" si="14"/>
+        <v>IG</v>
+      </c>
+      <c r="BG27">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="BH27">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="BI27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BK27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BN27">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="23">
+        <v>2</v>
+      </c>
+      <c r="E28" s="23">
+        <v>0</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" s="23">
+        <v>2</v>
+      </c>
+      <c r="K28" s="23">
+        <v>0</v>
+      </c>
+      <c r="L28" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="P28" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="23">
+        <v>0</v>
+      </c>
+      <c r="R28" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="BF28" s="25" t="str">
+        <f t="shared" si="14"/>
+        <v>RRQ T</v>
+      </c>
+      <c r="BG28">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BH28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BJ28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="BL28">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BM28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>2</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>2</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF29" s="25" t="str">
+        <f t="shared" si="14"/>
+        <v>SRG</v>
+      </c>
+      <c r="BG29">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
+      <c r="BH29">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BI29">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BJ29">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="BK29">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BM29">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="BN29">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:66" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="4"/>
+      <c r="C30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="5">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="5">
+        <v>2</v>
+      </c>
+      <c r="K30" s="5">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N30" s="4"/>
+      <c r="O30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P30" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>2</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF30" s="25" t="str">
+        <f t="shared" si="14"/>
+        <v>T. FLASH</v>
+      </c>
+      <c r="BG30">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
+      <c r="BH30">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BI30">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BJ30">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BK30">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BN30">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="23">
+        <v>2</v>
+      </c>
+      <c r="E31" s="23">
+        <v>1</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="23">
+        <v>2</v>
+      </c>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="O31" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="P31" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="23">
+        <v>1</v>
+      </c>
+      <c r="R31" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF31" s="25" t="str">
+        <f t="shared" si="14"/>
+        <v>T. REY</v>
+      </c>
+      <c r="BG31">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="BH31">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BI31">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BJ31">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BK31">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BL31">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BM31">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:66" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>2</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF32" s="25" t="str">
+        <f t="shared" si="14"/>
+        <v>T. VAMOS</v>
+      </c>
+      <c r="BG32">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="BH32">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BI32">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BJ32">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BK32">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="BM32">
+        <f>SUMPRODUCT(($C$14:$C$22=$BF32)*($F$14:$F$22=BM$24)*$D$14:$D$22)+SUMPRODUCT(($F$14:$F$22=$BF32)*($C$14:$C$22=BM$24)*$E$14:$E$22)+SUMPRODUCT(($I$14:$I$22=$BF32)*($L$14:$L$22=BM$24)*$J$14:$J$22)+SUMPRODUCT(($L$14:$L$22=$BF32)*($I$14:$I$22=BM$24)*$K$14:$K$22)+SUMPRODUCT(($O$14:$O$22=$BF32)*($R$14:$R$22=BM$24)*$P$14:$P$22)+SUMPRODUCT(($R$14:$R$22=$BF32)*($O$14:$O$22=BM$24)*$Q$14:$Q$22)+SUMPRODUCT(($C$25:$C$33=$BF32)*($F$25:$F$33=BM$24)*$D$25:$D$33)+SUMPRODUCT(($F$25:$F$33=$BF32)*($C$25:$C$33=BM$24)*$E$25:$E$33)+SUMPRODUCT(($I$25:$I$33=$BF32)*($L$25:$L$33=BM$24)*$J$25:$J$33)+SUMPRODUCT(($L$25:$L$33=$BF32)*($I$25:$I$33=BM$24)*$K$25:$K$33)+SUMPRODUCT(($O$25:$O$33=$BF32)*($R$25:$R$33=BM$24)*$P$25:$P$33)+SUMPRODUCT(($R$25:$R$33=$BF32)*($O$25:$O$33=BM$24)*$Q$25:$Q$33)+SUMPRODUCT(($C$36:$C$44=$BF32)*($F$36:$F$44=BM$24)*$D$36:$D$44)+SUMPRODUCT(($F$36:$F$44=$BF32)*($C$36:$C$44=BM$24)*$E$36:$E$44)+SUMPRODUCT(($I$36:$I$44=$BF32)*($L$36:$L$44=BM$24)*$J$36:$J$44)+SUMPRODUCT(($L$36:$L$44=$BF32)*($I$36:$I$44=BM$24)*$K$36:$K$44)+SUMPRODUCT(($O$36:$O$44=$BF32)*($R$36:$R$44=BM$24)*$P$36:$P$44)+SUMPRODUCT(($R$36:$R$44=$BF32)*($O$36:$O$44=BM$24)*$Q$36:$Q$44)</f>
+        <v>2</v>
+      </c>
+      <c r="BN32">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="6"/>
+    </row>
+    <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="88"/>
+      <c r="H35" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="88"/>
+      <c r="N35" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="O35" s="87"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="87"/>
+      <c r="R35" s="88"/>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B36" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="N36" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="24"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="6"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B39" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N39" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="24"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B40" s="2"/>
+      <c r="C40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="4"/>
+      <c r="C41" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N41" s="4"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="6"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B42" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="N42" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="24"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B43" s="2"/>
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="4"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="6"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="6"/>
+    </row>
+    <row r="45" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
+      <c r="H46" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="69"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="70"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="3"/>
+      <c r="H47" s="9"/>
+      <c r="R47" s="10"/>
+    </row>
+    <row r="48" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="3"/>
+      <c r="H48" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="80"/>
+      <c r="J48" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" s="82"/>
+      <c r="L48" s="82"/>
+      <c r="R48" s="10"/>
+    </row>
+    <row r="49" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="3"/>
+      <c r="H49" s="17" t="str">
+        <f>B5</f>
+        <v>T. VAMOS</v>
+      </c>
+      <c r="I49" s="37"/>
+      <c r="J49" s="71" t="str">
+        <f>B4</f>
+        <v>T. REY</v>
+      </c>
+      <c r="K49" s="72"/>
+      <c r="L49" s="37"/>
+      <c r="M49" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
+      <c r="R49" s="10"/>
+    </row>
+    <row r="50" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="3"/>
+      <c r="H50" s="18" t="str">
+        <f>B8</f>
+        <v>T. FLASH</v>
+      </c>
+      <c r="I50" s="38"/>
+      <c r="J50" s="71" t="str">
+        <f>IF(I49&gt;I50, H49, H50)</f>
+        <v>T. FLASH</v>
+      </c>
+      <c r="K50" s="72"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="105" t="str">
+        <f>IF((L49&gt;L50),J49,J50)</f>
+        <v>T. FLASH</v>
+      </c>
+      <c r="N50" s="106"/>
+      <c r="O50" s="37"/>
+      <c r="P50" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="78"/>
+    </row>
+    <row r="51" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="3"/>
+      <c r="H51" s="18" t="str">
+        <f>B6</f>
+        <v>IG</v>
+      </c>
+      <c r="I51" s="37"/>
+      <c r="J51" s="71" t="str">
+        <f>B3</f>
+        <v>SRG</v>
+      </c>
+      <c r="K51" s="72"/>
+      <c r="L51" s="37"/>
+      <c r="M51" s="105" t="str">
+        <f>IF((L51&gt;L52),J51,J52)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="N51" s="106"/>
+      <c r="O51" s="38"/>
+      <c r="P51" s="73" t="str">
+        <f>IF((O50&gt;O51),M50,M51)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="Q51" s="74"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="9"/>
+    </row>
+    <row r="52" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="3"/>
+      <c r="H52" s="18" t="str">
+        <f>B7</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="I52" s="38"/>
+      <c r="J52" s="71" t="str">
+        <f>IF(I51&gt;I52, H51, H52)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="K52" s="72"/>
+      <c r="L52" s="38"/>
+      <c r="M52" s="66" t="str">
+        <f>IF((O50&lt;O51),M50,M51)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="N52" s="67"/>
+      <c r="O52" s="37"/>
+      <c r="P52" s="73" t="str">
+        <f>IF((O52&gt;O53),M52,M53)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="Q52" s="74"/>
+      <c r="R52" s="45"/>
+      <c r="S52" s="9"/>
+    </row>
+    <row r="53" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="3"/>
+      <c r="H53" s="79" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="80"/>
+      <c r="J53" s="75" t="str">
+        <f>IF((L49&lt;L50),J49,J50)</f>
+        <v>T. FLASH</v>
+      </c>
+      <c r="K53" s="76"/>
+      <c r="L53" s="37"/>
+      <c r="M53" s="66" t="str">
+        <f>IF((L53&gt;L54),J53,J54)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="N53" s="67"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="R53" s="16"/>
+    </row>
+    <row r="54" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="3"/>
+      <c r="H54" s="9"/>
+      <c r="J54" s="75" t="str">
+        <f>IF((L51&lt;L52),J51,J52)</f>
+        <v>BTR MY</v>
+      </c>
+      <c r="K54" s="76"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="102" t="s">
+        <v>18</v>
+      </c>
+      <c r="N54" s="103"/>
+      <c r="O54" s="104"/>
+      <c r="R54" s="10"/>
+    </row>
+    <row r="55" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="H55" s="9"/>
+      <c r="J55" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
+      <c r="R55" s="10"/>
+    </row>
+    <row r="56" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H56" s="11"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="12"/>
+      <c r="P56" s="12"/>
+      <c r="Q56" s="12"/>
+      <c r="R56" s="13"/>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="H59" s="43"/>
+      <c r="J59" s="91"/>
+      <c r="K59" s="91"/>
+    </row>
+    <row r="61" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="H61" s="43"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -7629,2545 +10375,10 @@
     <mergeCell ref="N13:R13"/>
   </mergeCells>
   <conditionalFormatting sqref="C14:C22">
-    <cfRule type="expression" dxfId="84" priority="39">
+    <cfRule type="expression" dxfId="43" priority="39">
       <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&lt;$E14)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="40">
-      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&gt;$E14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C25:C33">
-    <cfRule type="expression" dxfId="82" priority="35">
-      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$D25&lt;$E25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="36">
-      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$D25&gt;$E25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C36:C44">
-    <cfRule type="expression" dxfId="80" priority="19">
-      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$D36&lt;$E36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="20">
-      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$D36&gt;$E36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C55">
-    <cfRule type="expression" dxfId="78" priority="15">
-      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$D47&lt;$E47)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="16">
-      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$D47&gt;$E47)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F22">
-    <cfRule type="expression" dxfId="76" priority="37">
-      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$E14&lt;$D14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="38">
-      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$E14&gt;$D14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:F33">
-    <cfRule type="expression" dxfId="74" priority="33">
-      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$E25&lt;$D25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="34">
-      <formula>AND(ISNUMBER($D25),ISNUMBER($E25),$E25&gt;$D25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F44">
-    <cfRule type="expression" dxfId="72" priority="17">
-      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$E36&lt;$D36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="18">
-      <formula>AND(ISNUMBER($D36),ISNUMBER($E36),$E36&gt;$D36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F47:F55">
-    <cfRule type="expression" dxfId="70" priority="13">
-      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$E47&lt;$D47)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="14">
-      <formula>AND(ISNUMBER($D47),ISNUMBER($E47),$E47&gt;$D47)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I22">
-    <cfRule type="expression" dxfId="68" priority="31">
-      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="32">
-      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25:I33">
-    <cfRule type="expression" dxfId="66" priority="27">
-      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="28">
-      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I36:I44">
-    <cfRule type="expression" dxfId="64" priority="23">
-      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&lt;$K36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="24">
-      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L14:L22">
-    <cfRule type="expression" dxfId="62" priority="29">
-      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="30">
-      <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L25:L33">
-    <cfRule type="expression" dxfId="60" priority="25">
-      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="26">
-      <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L36:L44">
-    <cfRule type="expression" dxfId="58" priority="21">
-      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="22">
-      <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&lt;$K36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O14:O22">
-    <cfRule type="expression" dxfId="56" priority="11">
-      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="12">
-      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O25:O33">
-    <cfRule type="expression" dxfId="54" priority="7">
-      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="8">
-      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O36:O44">
-    <cfRule type="expression" dxfId="52" priority="3">
-      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="4">
-      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R14:R22">
-    <cfRule type="expression" dxfId="50" priority="9">
-      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="10">
-      <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R25:R33">
-    <cfRule type="expression" dxfId="48" priority="5">
-      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="6">
-      <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R36:R44">
-    <cfRule type="expression" dxfId="46" priority="1">
-      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="2">
-      <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I49:I52 L49:L54 O50:O51" xr:uid="{2AC35715-5126-4C8B-836F-977311BB5FC7}">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O52:O53 R51:R52" xr:uid="{83DD0C4F-2D9C-477E-B1A0-35299695F693}">
-      <formula1>"0,1,2,3,4"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:E22 D25:E33 J14:K22 J25:K33 J36:K44 D36:E44 D47:E55 P14:Q22 P25:Q33 P36:Q44" xr:uid="{84190180-2645-4B02-8CB0-15E965C4AB48}">
-      <formula1>"0,1,2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C22 F14:F22 C25:C33 F25:F33 I14:I22 L14:L22 I25:I33 L25:L33 I36:I44 L36:L44 C36:C44 F36:F44 C47:C55 F47:F55 O14:O22 R14:R22 O25:O33 R25:R33 O36:O44 R36:R44" xr:uid="{354B0928-FEA4-44A4-91F9-500AA7B5A44B}">
-      <formula1>$B$3:$B$11</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" fitToWidth="0" orientation="landscape" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6A8B90-D2C1-45A7-9AC6-2CD09BC77B54}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BO61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" customWidth="1"/>
-    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="7.85546875" customWidth="1"/>
-    <col min="58" max="58" width="11" hidden="1" customWidth="1"/>
-    <col min="59" max="61" width="7.85546875" hidden="1" customWidth="1"/>
-    <col min="62" max="65" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="66" max="66" width="4.7109375" hidden="1" customWidth="1"/>
-    <col min="67" max="67" width="9.140625" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:67" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="70"/>
-      <c r="I1" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="8"/>
-      <c r="BF1" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="BG1" s="25">
-        <f>SUMPRODUCT(($C$14:$C$22=$BF1)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF1)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF1)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF1)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF1)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF1)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF1)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF1)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF1)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF1)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF1)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF1)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF1)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF1)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF1)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF1)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF1)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF1)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>8</v>
-      </c>
-      <c r="BH1" s="25">
-        <f>SUMPRODUCT(($C$14:$C$22=$BF1)*($D$14:$D$22-$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF1)*($E$14:$E$22-$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF1)*($J$14:$J$22-$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF1)*($K$14:$K$22-$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF1)*($P$14:$P$22-$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF1)*($Q$14:$Q$22-$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF1)*($D$25:$D$33-$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF1)*($E$25:$E$33-$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF1)*($J$25:$J$33-$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF1)*($K$25:$K$33-$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF1)*($P$25:$P$33-$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF1)*($Q$25:$Q$33-$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF1)*($D$36:$D$44-$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF1)*($E$36:$E$44-$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF1)*($J$36:$J$44-$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF1)*($K$36:$K$44-$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF1)*($P$36:$P$44-$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF1)*($Q$36:$Q$44-$P$36:$P$44))+SUMPRODUCT(($C$47:$C$55=$BF1)*($D$47:$D$55-$E$47:$E$55))+SUMPRODUCT(($F$47:$F$55=$BF1)*($E$47:$E$55-$D$47:$D$55))</f>
-        <v>10</v>
-      </c>
-      <c r="BI1" s="25">
-        <f t="shared" ref="BI1:BI9" si="0">IF(COUNTIFS($BG$1:$BG$9,BG1,$BH$1:$BH$9,BH1)&lt;=1,0,SUMPRODUCT(INDEX($BG$13:$BO$21,MATCH(BF1,$BF$13:$BF$21,0),0)*TRANSPOSE(($BG$1:$BG$9=BG1)*($BH$1:$BH$9=BH1))))</f>
-        <v>8</v>
-      </c>
-      <c r="BJ1" s="25">
-        <f t="shared" ref="BJ1:BJ9" si="1">1+SUMPRODUCT(--($BG$1:$BG$9&gt;BG1))+SUMPRODUCT(--($BG$1:$BG$9=BG1),--($BH$1:$BH$9&gt;BH1))+SUMPRODUCT(--($BG$1:$BG$9=BG1),--($BH$1:$BH$9=BH1),--($BI$1:$BI$9&gt;BI1))+SUMPRODUCT(--($BG$1:$BG$9=BG1),--($BH$1:$BH$9=BH1),--($BI$1:$BI$9=BI1),--($BF$1:$BF$9&lt;BF1))</f>
-        <v>2</v>
-      </c>
-      <c r="BL1" s="25"/>
-    </row>
-    <row r="2" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="BF2" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="BG2" s="25">
-        <f t="shared" ref="BG2:BG9" si="2">SUMPRODUCT(($C$14:$C$22=$BF2)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF2)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF2)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF2)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF2)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF2)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF2)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF2)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF2)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF2)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF2)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF2)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF2)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF2)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF2)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF2)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF2)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF2)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>5</v>
-      </c>
-      <c r="BH2" s="25">
-        <f t="shared" ref="BH2:BH9" si="3">SUMPRODUCT(($C$14:$C$22=$BF2)*($D$14:$D$22-$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF2)*($E$14:$E$22-$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF2)*($J$14:$J$22-$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF2)*($K$14:$K$22-$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF2)*($P$14:$P$22-$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF2)*($Q$14:$Q$22-$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF2)*($D$25:$D$33-$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF2)*($E$25:$E$33-$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF2)*($J$25:$J$33-$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF2)*($K$25:$K$33-$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF2)*($P$25:$P$33-$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF2)*($Q$25:$Q$33-$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$BF2)*($D$36:$D$44-$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$BF2)*($E$36:$E$44-$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$BF2)*($J$36:$J$44-$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$BF2)*($K$36:$K$44-$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$BF2)*($P$36:$P$44-$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$BF2)*($Q$36:$Q$44-$P$36:$P$44))+SUMPRODUCT(($C$47:$C$55=$BF2)*($D$47:$D$55-$E$47:$E$55))+SUMPRODUCT(($F$47:$F$55=$BF2)*($E$47:$E$55-$D$47:$D$55))</f>
-        <v>-2</v>
-      </c>
-      <c r="BI2" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ2" s="25">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="BL2" s="25"/>
-    </row>
-    <row r="3" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="str">
-        <f t="shared" ref="B3:B11" si="4">INDEX($BF$1:$BF$9,MATCH(ROW()-2,$BJ$1:$BJ$9,0))</f>
-        <v>TLID</v>
-      </c>
-      <c r="C3" s="29">
-        <f>SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>9</v>
-      </c>
-      <c r="D3" s="29">
-        <f>SUMPRODUCT(($C$14:$C$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B3)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B3)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B3)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B3)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B3)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B3)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B3)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B3)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B3)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
-        <v>2</v>
-      </c>
-      <c r="E3" s="29">
-        <f>SUMIF($C$14:$C$22,$B3,$D$14:$D$22)+SUMIF($F$14:$F$22,$B3,$E$14:$E$22)+SUMIF($I$14:$I$22,$B3,$J$14:$J$22)+SUMIF($L$14:$L$22,$B3,$K$14:$K$22)+SUMIF($O$14:$O$22,$B3,$P$14:$P$22)+SUMIF($R$14:$R$22,$B3,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B3,$D$25:$D$33)+SUMIF($F$25:$F$33,$B3,$E$25:$E$33)+SUMIF($I$25:$I$33,$B3,$J$25:$J$33)+SUMIF($L$25:$L$33,$B3,$K$25:$K$33)+SUMIF($O$25:$O$33,$B3,$P$25:$P$33)+SUMIF($R$25:$R$33,$B3,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B3,$D$36:$D$44)+SUMIF($F$36:$F$44,$B3,$E$36:$E$44)+SUMIF($I$36:$I$44,$B3,$J$36:$J$44)+SUMIF($L$36:$L$44,$B3,$K$36:$K$44)+SUMIF($O$36:$O$44,$B3,$P$36:$P$44)+SUMIF($R$36:$R$44,$B3,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
-        <v>19</v>
-      </c>
-      <c r="F3" s="29">
-        <f>SUMIF($C$14:$C$22,$B3,$E$14:$E$22)+SUMIF($F$14:$F$22,$B3,$D$14:$D$22)+SUMIF($I$14:$I$22,$B3,$K$14:$K$22)+SUMIF($L$14:$L$22,$B3,$J$14:$J$22)+SUMIF($O$14:$O$22,$B3,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B3,$P$14:$P$22)+SUMIF($C$25:$C$33,$B3,$E$25:$E$33)+SUMIF($F$25:$F$33,$B3,$D$25:$D$33)+SUMIF($I$25:$I$33,$B3,$K$25:$K$33)+SUMIF($L$25:$L$33,$B3,$J$25:$J$33)+SUMIF($O$25:$O$33,$B3,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B3,$P$25:$P$33)+SUMIF($C$36:$C$44,$B3,$E$36:$E$44)+SUMIF($F$36:$F$44,$B3,$D$36:$D$44)+SUMIF($I$36:$I$44,$B3,$K$36:$K$44)+SUMIF($L$36:$L$44,$B3,$J$36:$J$44)+SUMIF($O$36:$O$44,$B3,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B3,$P$36:$P$44)+SUMIF($C$47:$C$55,$B3,$E$47:$E$55)+SUMIF($F$47:$F$55,$B3,$D$47:$D$55)</f>
-        <v>7</v>
-      </c>
-      <c r="G3" s="30">
-        <f t="shared" ref="G3:G11" si="5">E3-F3</f>
-        <v>12</v>
-      </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="61"/>
-      <c r="BF3" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="BG3" s="25">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="BH3" s="25">
-        <f t="shared" si="3"/>
-        <v>-5</v>
-      </c>
-      <c r="BI3" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ3" s="25">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="BL3" s="25"/>
-    </row>
-    <row r="4" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
-        <v>2</v>
-      </c>
-      <c r="B4" s="28" t="str">
-        <f t="shared" si="4"/>
-        <v>AE</v>
-      </c>
-      <c r="C4" s="29">
-        <f t="shared" ref="C4:C11" si="6">SUMPRODUCT(($C$14:$C$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&gt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&gt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&gt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&gt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&gt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&gt;$P$36:$P$44))</f>
-        <v>8</v>
-      </c>
-      <c r="D4" s="29">
-        <f t="shared" ref="D4:D11" si="7">SUMPRODUCT(($C$14:$C$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($D$14:$D$22&lt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$B4)*ISNUMBER($D$14:$D$22)*ISNUMBER($E$14:$E$22)*($E$14:$E$22&lt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($J$14:$J$22&lt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$B4)*ISNUMBER($J$14:$J$22)*ISNUMBER($K$14:$K$22)*($K$14:$K$22&lt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($P$14:$P$22&lt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$B4)*ISNUMBER($P$14:$P$22)*ISNUMBER($Q$14:$Q$22)*($Q$14:$Q$22&lt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($D$25:$D$33&lt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$B4)*ISNUMBER($D$25:$D$33)*ISNUMBER($E$25:$E$33)*($E$25:$E$33&lt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($J$25:$J$33&lt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$B4)*ISNUMBER($J$25:$J$33)*ISNUMBER($K$25:$K$33)*($K$25:$K$33&lt;$J$25:$K$33))+SUMPRODUCT(($O$25:$O$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($P$25:$P$33&lt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$B4)*ISNUMBER($P$25:$P$33)*ISNUMBER($Q$25:$Q$33)*($Q$25:$Q$33&lt;$P$25:$P$33))+SUMPRODUCT(($C$36:$C$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($D$36:$D$44&lt;$E$36:$E$44))+SUMPRODUCT(($F$36:$F$44=$B4)*ISNUMBER($D$36:$D$44)*ISNUMBER($E$36:$E$44)*($E$36:$E$44&lt;$D$36:$D$44))+SUMPRODUCT(($I$36:$I$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($J$36:$J$44&lt;$K$36:$K$44))+SUMPRODUCT(($L$36:$L$44=$B4)*ISNUMBER($J$36:$J$44)*ISNUMBER($K$36:$K$44)*($K$36:$K$44&lt;$J$36:$J$44))+SUMPRODUCT(($O$36:$O$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($P$36:$P$44&lt;$Q$36:$Q$44))+SUMPRODUCT(($R$36:$R$44=$B4)*ISNUMBER($P$36:$P$44)*ISNUMBER($Q$36:$Q$44)*($Q$36:$Q$44&lt;$P$36:$P$44))</f>
-        <v>3</v>
-      </c>
-      <c r="E4" s="29">
-        <f>SUMIF($C$14:$C$22,$B4,$D$14:$D$22)+SUMIF($F$14:$F$22,$B4,$E$14:$E$22)+SUMIF($I$14:$I$22,$B4,$J$14:$J$22)+SUMIF($L$14:$L$22,$B4,$K$14:$K$22)+SUMIF($O$14:$O$22,$B4,$P$14:$P$22)+SUMIF($R$14:$R$22,$B4,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B4,$D$25:$D$33)+SUMIF($F$25:$F$33,$B4,$E$25:$E$33)+SUMIF($I$25:$I$33,$B4,$J$25:$J$33)+SUMIF($L$25:$L$33,$B4,$K$25:$K$33)+SUMIF($O$25:$O$33,$B4,$P$25:$P$33)+SUMIF($R$25:$R$33,$B4,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B4,$D$36:$D$44)+SUMIF($F$36:$F$44,$B4,$E$36:$E$44)+SUMIF($I$36:$I$44,$B4,$J$36:$J$44)+SUMIF($L$36:$L$44,$B4,$K$36:$K$44)+SUMIF($O$36:$O$44,$B4,$P$36:$P$44)+SUMIF($R$36:$R$44,$B4,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B4,$D$47:$D$55)+SUMIF($F$47:$F$55,$B4,$E$47:$E$55)</f>
-        <v>17</v>
-      </c>
-      <c r="F4" s="29">
-        <f>SUMIF($C$14:$C$22,$B4,$E$14:$E$22)+SUMIF($F$14:$F$22,$B4,$D$14:$D$22)+SUMIF($I$14:$I$22,$B4,$K$14:$K$22)+SUMIF($L$14:$L$22,$B4,$J$14:$J$22)+SUMIF($O$14:$O$22,$B4,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B4,$P$14:$P$22)+SUMIF($C$25:$C$33,$B4,$E$25:$E$33)+SUMIF($F$25:$F$33,$B4,$D$25:$D$33)+SUMIF($I$25:$I$33,$B4,$K$25:$K$33)+SUMIF($L$25:$L$33,$B4,$J$25:$J$33)+SUMIF($O$25:$O$33,$B4,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B4,$P$25:$P$33)+SUMIF($C$36:$C$44,$B4,$E$36:$E$44)+SUMIF($F$36:$F$44,$B4,$D$36:$D$44)+SUMIF($I$36:$I$44,$B4,$K$36:$K$44)+SUMIF($L$36:$L$44,$B4,$J$36:$J$44)+SUMIF($O$36:$O$44,$B4,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B4,$P$36:$P$44)+SUMIF($C$47:$C$55,$B4,$E$47:$E$55)+SUMIF($F$47:$F$55,$B4,$D$47:$D$55)</f>
-        <v>7</v>
-      </c>
-      <c r="G4" s="30">
-        <f t="shared" si="5"/>
-        <v>10</v>
-      </c>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="61"/>
-      <c r="BF4" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="BG4" s="25">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="BH4" s="25">
-        <f t="shared" si="3"/>
-        <v>-1</v>
-      </c>
-      <c r="BI4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ4" s="25">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="BL4" s="25"/>
-    </row>
-    <row r="5" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="54">
-        <v>3</v>
-      </c>
-      <c r="B5" s="48" t="str">
-        <f t="shared" si="4"/>
-        <v>NAVI</v>
-      </c>
-      <c r="C5" s="49">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="D5" s="49">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="E5" s="49">
-        <f>SUMIF($C$14:$C$22,$B5,$D$14:$D$22)+SUMIF($F$14:$F$22,$B5,$E$14:$E$22)+SUMIF($I$14:$I$22,$B5,$J$14:$J$22)+SUMIF($L$14:$L$22,$B5,$K$14:$K$22)+SUMIF($O$14:$O$22,$B5,$P$14:$P$22)+SUMIF($R$14:$R$22,$B5,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B5,$D$25:$D$33)+SUMIF($F$25:$F$33,$B5,$E$25:$E$33)+SUMIF($I$25:$I$33,$B5,$J$25:$J$33)+SUMIF($L$25:$L$33,$B5,$K$25:$K$33)+SUMIF($O$25:$O$33,$B5,$P$25:$P$33)+SUMIF($R$25:$R$33,$B5,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B5,$D$36:$D$44)+SUMIF($F$36:$F$44,$B5,$E$36:$E$44)+SUMIF($I$36:$I$44,$B5,$J$36:$J$44)+SUMIF($L$36:$L$44,$B5,$K$36:$K$44)+SUMIF($O$36:$O$44,$B5,$P$36:$P$44)+SUMIF($R$36:$R$44,$B5,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
-        <v>16</v>
-      </c>
-      <c r="F5" s="49">
-        <f t="shared" ref="F5:F11" si="8">SUMIF($C$14:$C$22,$B5,$E$14:$E$22)+SUMIF($F$14:$F$22,$B5,$D$14:$D$22)+SUMIF($I$14:$I$22,$B5,$K$14:$K$22)+SUMIF($L$14:$L$22,$B5,$J$14:$J$22)+SUMIF($O$14:$O$22,$B5,$Q$14:$Q$22)+SUMIF($R$14:$R$22,$B5,$P$14:$P$22)+SUMIF($C$25:$C$33,$B5,$E$25:$E$33)+SUMIF($F$25:$F$33,$B5,$D$25:$D$33)+SUMIF($I$25:$I$33,$B5,$K$25:$K$33)+SUMIF($L$25:$L$33,$B5,$J$25:$J$33)+SUMIF($O$25:$O$33,$B5,$Q$25:$Q$33)+SUMIF($R$25:$R$33,$B5,$P$25:$P$33)+SUMIF($C$36:$C$44,$B5,$E$36:$E$44)+SUMIF($F$36:$F$44,$B5,$D$36:$D$44)+SUMIF($I$36:$I$44,$B5,$K$36:$K$44)+SUMIF($L$36:$L$44,$B5,$J$36:$J$44)+SUMIF($O$36:$O$44,$B5,$Q$36:$Q$44)+SUMIF($R$36:$R$44,$B5,$P$36:$P$44)+SUMIF($C$47:$C$55,$B5,$E$47:$E$55)+SUMIF($F$47:$F$55,$B5,$D$47:$D$55)</f>
-        <v>6</v>
-      </c>
-      <c r="G5" s="50">
-        <f t="shared" si="5"/>
-        <v>10</v>
-      </c>
-      <c r="I5" s="59"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="61"/>
-      <c r="BF5" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="BG5" s="25">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="BH5" s="25">
-        <f t="shared" si="3"/>
-        <v>-12</v>
-      </c>
-      <c r="BI5" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ5" s="25">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="BL5" s="25"/>
-    </row>
-    <row r="6" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53">
-        <v>4</v>
-      </c>
-      <c r="B6" s="46" t="str">
-        <f t="shared" si="4"/>
-        <v>EVOS</v>
-      </c>
-      <c r="C6" s="51">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="D6" s="51">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="E6" s="51">
-        <f t="shared" ref="E6:E8" si="9">SUMIF($C$14:$C$22,$B6,$D$14:$D$22)+SUMIF($F$14:$F$22,$B6,$E$14:$E$22)+SUMIF($I$14:$I$22,$B6,$J$14:$J$22)+SUMIF($L$14:$L$22,$B6,$K$14:$K$22)+SUMIF($O$14:$O$22,$B6,$P$14:$P$22)+SUMIF($R$14:$R$22,$B6,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B6,$D$25:$D$33)+SUMIF($F$25:$F$33,$B6,$E$25:$E$33)+SUMIF($I$25:$I$33,$B6,$J$25:$J$33)+SUMIF($L$25:$L$33,$B6,$K$25:$K$33)+SUMIF($O$25:$O$33,$B6,$P$25:$P$33)+SUMIF($R$25:$R$33,$B6,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B6,$D$36:$D$44)+SUMIF($F$36:$F$44,$B6,$E$36:$E$44)+SUMIF($I$36:$I$44,$B6,$J$36:$J$44)+SUMIF($L$36:$L$44,$B6,$K$36:$K$44)+SUMIF($O$36:$O$44,$B6,$P$36:$P$44)+SUMIF($R$36:$R$44,$B6,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B4,$D$47:$D$55)+SUMIF($F$47:$F$55,$B4,$E$47:$E$55)</f>
-        <v>11</v>
-      </c>
-      <c r="F6" s="51">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="G6" s="52">
-        <f t="shared" si="5"/>
-        <v>-1</v>
-      </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="61"/>
-      <c r="BF6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="BG6" s="25">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="BH6" s="25">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="BI6" s="25">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="BJ6" s="25">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="BL6" s="25"/>
-    </row>
-    <row r="7" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="53">
-        <v>5</v>
-      </c>
-      <c r="B7" s="47" t="str">
-        <f t="shared" si="4"/>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="C7" s="51">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="D7" s="51">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="E7" s="51">
-        <f t="shared" si="9"/>
-        <v>11</v>
-      </c>
-      <c r="F7" s="51">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="G7" s="52">
-        <f t="shared" si="5"/>
-        <v>-2</v>
-      </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="61"/>
-      <c r="BF7" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG7" s="25">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="BH7" s="25">
-        <f t="shared" si="3"/>
-        <v>-2</v>
-      </c>
-      <c r="BI7" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ7" s="25">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="BL7" s="25"/>
-    </row>
-    <row r="8" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="54">
-        <v>6</v>
-      </c>
-      <c r="B8" s="48" t="str">
-        <f t="shared" si="4"/>
-        <v>ONIC</v>
-      </c>
-      <c r="C8" s="49">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="D8" s="49">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="E8" s="49">
-        <f t="shared" si="9"/>
-        <v>12</v>
-      </c>
-      <c r="F8" s="49">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="G8" s="50">
-        <f t="shared" si="5"/>
-        <v>-2</v>
-      </c>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="61"/>
-      <c r="BF8" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="BG8" s="25">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="BH8" s="25">
-        <f t="shared" si="3"/>
-        <v>-10</v>
-      </c>
-      <c r="BI8" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ8" s="25">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="BL8" s="25"/>
-    </row>
-    <row r="9" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="31">
-        <v>7</v>
-      </c>
-      <c r="B9" s="32" t="str">
-        <f t="shared" si="4"/>
-        <v>DEWA</v>
-      </c>
-      <c r="C9" s="39">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="D9" s="39">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E9" s="39">
-        <f>SUMIF($C$14:$C$22,$B9,$D$14:$D$22)+SUMIF($F$14:$F$22,$B9,$E$14:$E$22)+SUMIF($I$14:$I$22,$B9,$J$14:$J$22)+SUMIF($L$14:$L$22,$B9,$K$14:$K$22)+SUMIF($O$14:$O$22,$B9,$P$14:$P$22)+SUMIF($R$14:$R$22,$B9,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B9,$D$25:$D$33)+SUMIF($F$25:$F$33,$B9,$E$25:$E$33)+SUMIF($I$25:$I$33,$B9,$J$25:$J$33)+SUMIF($L$25:$L$33,$B9,$K$25:$K$33)+SUMIF($O$25:$O$33,$B9,$P$25:$P$33)+SUMIF($R$25:$R$33,$B9,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B9,$D$36:$D$44)+SUMIF($F$36:$F$44,$B9,$E$36:$E$44)+SUMIF($I$36:$I$44,$B9,$J$36:$J$44)+SUMIF($L$36:$L$44,$B9,$K$36:$K$44)+SUMIF($O$36:$O$44,$B9,$P$36:$P$44)+SUMIF($R$36:$R$44,$B9,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B3,$D$47:$D$55)+SUMIF($F$47:$F$55,$B3,$E$47:$E$55)</f>
-        <v>9</v>
-      </c>
-      <c r="F9" s="41">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="G9" s="33">
-        <f t="shared" si="5"/>
-        <v>-5</v>
-      </c>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="61"/>
-      <c r="BF9" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="BG9" s="25">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="BH9" s="25">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="BI9" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BJ9" s="25">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="BL9" s="25"/>
-    </row>
-    <row r="10" spans="1:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31">
-        <v>8</v>
-      </c>
-      <c r="B10" s="32" t="str">
-        <f t="shared" si="4"/>
-        <v>RRQ</v>
-      </c>
-      <c r="C10" s="39">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="D10" s="39">
-        <f t="shared" si="7"/>
-        <v>8</v>
-      </c>
-      <c r="E10" s="39">
-        <f t="shared" ref="E10:E11" si="10">SUMIF($C$14:$C$22,$B10,$D$14:$D$22)+SUMIF($F$14:$F$22,$B10,$E$14:$E$22)+SUMIF($I$14:$I$22,$B10,$J$14:$J$22)+SUMIF($L$14:$L$22,$B10,$K$14:$K$22)+SUMIF($O$14:$O$22,$B10,$P$14:$P$22)+SUMIF($R$14:$R$22,$B10,$Q$14:$Q$22)+SUMIF($C$25:$C$33,$B10,$D$25:$D$33)+SUMIF($F$25:$F$33,$B10,$E$25:$E$33)+SUMIF($I$25:$I$33,$B10,$J$25:$J$33)+SUMIF($L$25:$L$33,$B10,$K$25:$K$33)+SUMIF($O$25:$O$33,$B10,$P$25:$P$33)+SUMIF($R$25:$R$33,$B10,$Q$25:$Q$33)+SUMIF($C$36:$C$44,$B10,$D$36:$D$44)+SUMIF($F$36:$F$44,$B10,$E$36:$E$44)+SUMIF($I$36:$I$44,$B10,$J$36:$J$44)+SUMIF($L$36:$L$44,$B10,$K$36:$K$44)+SUMIF($O$36:$O$44,$B10,$P$36:$P$44)+SUMIF($R$36:$R$44,$B10,$Q$36:$Q$44)+SUMIF($C$47:$C$55,$B4,$D$47:$D$55)+SUMIF($F$47:$F$55,$B4,$E$47:$E$55)</f>
-        <v>7</v>
-      </c>
-      <c r="F10" s="41">
-        <f t="shared" si="8"/>
-        <v>17</v>
-      </c>
-      <c r="G10" s="33">
-        <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
-      <c r="I10" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="64"/>
-    </row>
-    <row r="11" spans="1:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34">
-        <v>9</v>
-      </c>
-      <c r="B11" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v>GEEK</v>
-      </c>
-      <c r="C11" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="D11" s="40">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="E11" s="40">
-        <f t="shared" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="F11" s="42">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-      <c r="G11" s="36">
-        <f t="shared" si="5"/>
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="BG12" t="s">
-        <v>20</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>21</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>22</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>38</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>23</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>24</v>
-      </c>
-      <c r="BN12" t="s">
-        <v>37</v>
-      </c>
-      <c r="BO12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="67"/>
-      <c r="H13" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="I13" s="66"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="67"/>
-      <c r="N13" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="67"/>
-      <c r="BF13" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="BG13">
-        <f>SUMPRODUCT(($C$14:$C$22=$BF13)*($F$14:$F$22=BG$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF13)*($C$14:$C$22=BG$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF13)*($L$14:$L$22=BG$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF13)*($I$14:$I$22=BG$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF13)*($R$14:$R$22=BG$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF13)*($O$14:$O$22=BG$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF13)*($F$25:$F$33=BG$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF13)*($C$25:$C$33=BG$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF13)*($L$25:$L$33=BG$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF13)*($I$25:$I$33=BG$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF13)*($R$25:$R$33=BG$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF13)*($O$25:$O$33=BG$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF13)*($F$37:$F$45=BG$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF13)*($C$37:$C$45=BG$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF13)*($L$37:$L$45=BG$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF13)*($I$37:$I$45=BG$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF13)*($R$37:$R$45=BG$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF13)*($O$37:$O$45=BG$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
-        <v>0</v>
-      </c>
-      <c r="BH13">
-        <f t="shared" ref="BH13:BO21" si="11">SUMPRODUCT(($C$14:$C$22=$BF13)*($F$14:$F$22=BH$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF13)*($C$14:$C$22=BH$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF13)*($L$14:$L$22=BH$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF13)*($I$14:$I$22=BH$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF13)*($R$14:$R$22=BH$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF13)*($O$14:$O$22=BH$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF13)*($F$25:$F$33=BH$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF13)*($C$25:$C$33=BH$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF13)*($L$25:$L$33=BH$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF13)*($I$25:$I$33=BH$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF13)*($R$25:$R$33=BH$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF13)*($O$25:$O$33=BH$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF13)*($F$37:$F$45=BH$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF13)*($C$37:$C$45=BH$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF13)*($L$37:$L$45=BH$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF13)*($I$37:$I$45=BH$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF13)*($R$37:$R$45=BH$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF13)*($O$37:$O$45=BH$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
-        <v>1</v>
-      </c>
-      <c r="BI13">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BJ13">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BK13">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BL13">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BM13">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BN13">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="BO13">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="23">
-        <v>2</v>
-      </c>
-      <c r="E14" s="23">
-        <v>0</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="23">
-        <v>0</v>
-      </c>
-      <c r="K14" s="23">
-        <v>2</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="23">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="23">
-        <v>0</v>
-      </c>
-      <c r="R14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="BF14" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="BG14">
-        <f t="shared" ref="BG14:BG21" si="12">SUMPRODUCT(($C$14:$C$22=$BF14)*($F$14:$F$22=BG$12)*($D$14:$D$22&gt;$E$14:$E$22))+SUMPRODUCT(($F$14:$F$22=$BF14)*($C$14:$C$22=BG$12)*($E$14:$E$22&gt;$D$14:$D$22))+SUMPRODUCT(($I$14:$I$22=$BF14)*($L$14:$L$22=BG$12)*($J$14:$J$22&gt;$K$14:$K$22))+SUMPRODUCT(($L$14:$L$22=$BF14)*($I$14:$I$22=BG$12)*($K$14:$K$22&gt;$J$14:$J$22))+SUMPRODUCT(($O$14:$O$22=$BF14)*($R$14:$R$22=BG$12)*($P$14:$P$22&gt;$Q$14:$Q$22))+SUMPRODUCT(($R$14:$R$22=$BF14)*($O$14:$O$22=BG$12)*($Q$14:$Q$22&gt;$P$14:$P$22))+SUMPRODUCT(($C$25:$C$33=$BF14)*($F$25:$F$33=BG$12)*($D$25:$D$33&gt;$E$25:$E$33))+SUMPRODUCT(($F$25:$F$33=$BF14)*($C$25:$C$33=BG$12)*($E$25:$E$33&gt;$D$25:$D$33))+SUMPRODUCT(($I$25:$I$33=$BF14)*($L$25:$L$33=BG$12)*($J$25:$J$33&gt;$K$25:$K$33))+SUMPRODUCT(($L$25:$L$33=$BF14)*($I$25:$I$33=BG$12)*($K$25:$K$33&gt;$J$25:$J$33))+SUMPRODUCT(($O$25:$O$33=$BF14)*($R$25:$R$33=BG$12)*($P$25:$P$33&gt;$Q$25:$Q$33))+SUMPRODUCT(($R$25:$R$33=$BF14)*($O$25:$O$33=BG$12)*($Q$25:$Q$33&gt;$P$25:$P$33))+SUMPRODUCT(($C$37:$C$45=$BF14)*($F$37:$F$45=BG$12)*($D$37:$D$45&gt;$E$37:$E$45))+SUMPRODUCT(($F$37:$F$45=$BF14)*($C$37:$C$45=BG$12)*($E$37:$E$45&gt;$D$37:$D$45))+SUMPRODUCT(($I$37:$I$45=$BF14)*($L$37:$L$45=BG$12)*($J$37:$J$45&gt;$K$37:$K$45))+SUMPRODUCT(($L$37:$L$45=$BF14)*($I$37:$I$45=BG$12)*($K$37:$K$45&gt;$J$37:$J$45))+SUMPRODUCT(($O$37:$O$45=$BF14)*($R$37:$R$45=BG$12)*($P$37:$P$45&gt;$Q$37:$Q$45))+SUMPRODUCT(($R$37:$R$45=$BF14)*($O$37:$O$45=BG$12)*($Q$37:$Q$45&gt;$P$37:$P$45))</f>
-        <v>0</v>
-      </c>
-      <c r="BH14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BI14">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BJ14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BK14">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BL14">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BM14">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BN14">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BO14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="1">
-        <v>2</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="BF15" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="BG15">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="BH15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BI15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BJ15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BK15">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BL15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM15">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BN15">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BO15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="6"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="6"/>
-      <c r="BF16" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="BG16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BI16">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BJ16">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BK16">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BL16">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BN16">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BO16">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="23">
-        <v>2</v>
-      </c>
-      <c r="E17" s="23">
-        <v>1</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="23">
-        <v>2</v>
-      </c>
-      <c r="K17" s="23">
-        <v>0</v>
-      </c>
-      <c r="L17" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O17" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="23">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="23">
-        <v>1</v>
-      </c>
-      <c r="R17" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="BF17" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="BG17">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BH17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BI17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BJ17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BK17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BL17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM17">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="BN17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BO17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" s="1">
-        <v>2</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P18" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="BF18" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="BG18">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BH18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BI18">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BJ18">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="BK18">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="BL18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM18">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BN18">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BO18">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:67" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4"/>
-      <c r="C19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
-        <v>2</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="5">
-        <v>2</v>
-      </c>
-      <c r="K19" s="5">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P19" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>2</v>
-      </c>
-      <c r="R19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="BF19" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG19">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="BH19">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BI19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BJ19">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BK19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BL19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BN19">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BO19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="23">
-        <v>2</v>
-      </c>
-      <c r="E20" s="23">
-        <v>0</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="23">
-        <v>0</v>
-      </c>
-      <c r="K20" s="23">
-        <v>2</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="23">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="23">
-        <v>0</v>
-      </c>
-      <c r="R20" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="BF20" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="BG20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BH20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BI20">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BJ20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BK20">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BL20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BN20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BO20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:67" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>2</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>2</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="BF21" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="BG21">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="BH21">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="BI21">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BJ21">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BK21">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="BL21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BM21">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BN21">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="BO21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="4"/>
-      <c r="C22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5">
-        <v>2</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <v>2</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="4"/>
-      <c r="O22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" s="5">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>1</v>
-      </c>
-      <c r="R22" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="2:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="65" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="67"/>
-      <c r="H24" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="67"/>
-      <c r="N24" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="67"/>
-    </row>
-    <row r="25" spans="2:67" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="23">
-        <v>2</v>
-      </c>
-      <c r="E25" s="23">
-        <v>0</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="J25" s="23">
-        <v>2</v>
-      </c>
-      <c r="K25" s="23">
-        <v>1</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="N25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="O25" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="P25" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="23">
-        <v>2</v>
-      </c>
-      <c r="R25" s="24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:67" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>2</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="2:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="6"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="6"/>
-    </row>
-    <row r="28" spans="2:67" x14ac:dyDescent="0.25">
-      <c r="B28" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="23">
-        <v>2</v>
-      </c>
-      <c r="E28" s="23">
-        <v>1</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="23">
-        <v>2</v>
-      </c>
-      <c r="K28" s="23">
-        <v>0</v>
-      </c>
-      <c r="L28" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O28" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="P28" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="23">
-        <v>2</v>
-      </c>
-      <c r="R28" s="24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="2:67" x14ac:dyDescent="0.25">
-      <c r="B29" s="2"/>
-      <c r="C29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="1">
-        <v>2</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P29" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>2</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="2:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="4"/>
-      <c r="C30" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="5">
-        <v>2</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J30" s="5">
-        <v>2</v>
-      </c>
-      <c r="K30" s="5">
-        <v>0</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N30" s="4"/>
-      <c r="O30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>2</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:67" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="23">
-        <v>0</v>
-      </c>
-      <c r="E31" s="23">
-        <v>2</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="J31" s="23">
-        <v>0</v>
-      </c>
-      <c r="K31" s="23">
-        <v>2</v>
-      </c>
-      <c r="L31" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="O31" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="P31" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="23">
-        <v>2</v>
-      </c>
-      <c r="R31" s="24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="2:67" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
-      <c r="C32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="1">
-        <v>0</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>2</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="4"/>
-      <c r="C33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5">
-        <v>2</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J33" s="5">
-        <v>1</v>
-      </c>
-      <c r="K33" s="5">
-        <v>2</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N33" s="4"/>
-      <c r="O33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P33" s="5">
-        <v>2</v>
-      </c>
-      <c r="Q33" s="5">
-        <v>1</v>
-      </c>
-      <c r="R33" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67"/>
-      <c r="H35" s="65" t="s">
-        <v>10</v>
-      </c>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="67"/>
-      <c r="N35" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="67"/>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="O36" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="2"/>
-      <c r="C37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H37" s="2"/>
-      <c r="I37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="4"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="6"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="6"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="N39" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O39" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="2"/>
-      <c r="C40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="4"/>
-      <c r="C41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" s="4"/>
-      <c r="O41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="N42" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="2"/>
-      <c r="C43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="4"/>
-      <c r="C44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N44" s="4"/>
-      <c r="O44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="58"/>
-      <c r="H46" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="I46" s="86"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="86"/>
-      <c r="M46" s="86"/>
-      <c r="N46" s="86"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="87"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="3"/>
-      <c r="H47" s="9"/>
-      <c r="R47" s="10"/>
-    </row>
-    <row r="48" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="3"/>
-      <c r="H48" s="92" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="93"/>
-      <c r="J48" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="K48" s="95"/>
-      <c r="L48" s="95"/>
-      <c r="R48" s="10"/>
-    </row>
-    <row r="49" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="3"/>
-      <c r="H49" s="17" t="str">
-        <f>B5</f>
-        <v>NAVI</v>
-      </c>
-      <c r="I49" s="37"/>
-      <c r="J49" s="81" t="str">
-        <f>B4</f>
-        <v>AE</v>
-      </c>
-      <c r="K49" s="82"/>
-      <c r="L49" s="37"/>
-      <c r="M49" s="94" t="s">
-        <v>50</v>
-      </c>
-      <c r="N49" s="94"/>
-      <c r="O49" s="94"/>
-      <c r="R49" s="10"/>
-    </row>
-    <row r="50" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="3"/>
-      <c r="H50" s="18" t="str">
-        <f>B8</f>
-        <v>ONIC</v>
-      </c>
-      <c r="I50" s="38"/>
-      <c r="J50" s="81" t="str">
-        <f>IF(I49&gt;I50, H49, H50)</f>
-        <v>ONIC</v>
-      </c>
-      <c r="K50" s="82"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="79" t="str">
-        <f>IF((L49&gt;L50),J49,J50)</f>
-        <v>ONIC</v>
-      </c>
-      <c r="N50" s="80"/>
-      <c r="O50" s="37"/>
-      <c r="P50" s="90" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q50" s="90"/>
-      <c r="R50" s="91"/>
-    </row>
-    <row r="51" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="3"/>
-      <c r="H51" s="18" t="str">
-        <f>B6</f>
-        <v>EVOS</v>
-      </c>
-      <c r="I51" s="37"/>
-      <c r="J51" s="81" t="str">
-        <f>B3</f>
-        <v>TLID</v>
-      </c>
-      <c r="K51" s="82"/>
-      <c r="L51" s="37"/>
-      <c r="M51" s="79" t="str">
-        <f>IF((L51&gt;L52),J51,J52)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="N51" s="80"/>
-      <c r="O51" s="38"/>
-      <c r="P51" s="88" t="str">
-        <f>IF((O50&gt;O51),M50,M51)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="Q51" s="89"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="9"/>
-    </row>
-    <row r="52" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="3"/>
-      <c r="H52" s="18" t="str">
-        <f>B7</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="I52" s="38"/>
-      <c r="J52" s="81" t="str">
-        <f>IF(I51&gt;I52, H51, H52)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="K52" s="82"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="83" t="str">
-        <f>IF((O50&lt;O51),M50,M51)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="N52" s="84"/>
-      <c r="O52" s="37"/>
-      <c r="P52" s="88" t="str">
-        <f>IF((O52&gt;O53),M52,M53)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="Q52" s="89"/>
-      <c r="R52" s="45"/>
-      <c r="S52" s="9"/>
-    </row>
-    <row r="53" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="3"/>
-      <c r="H53" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" s="93"/>
-      <c r="J53" s="73" t="str">
-        <f>IF((L49&lt;L50),J49,J50)</f>
-        <v>ONIC</v>
-      </c>
-      <c r="K53" s="74"/>
-      <c r="L53" s="37"/>
-      <c r="M53" s="83" t="str">
-        <f>IF((L53&gt;L54),J53,J54)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="N53" s="84"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="16"/>
-    </row>
-    <row r="54" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="3"/>
-      <c r="H54" s="9"/>
-      <c r="J54" s="73" t="str">
-        <f>IF((L51&lt;L52),J51,J52)</f>
-        <v>BTR by VIT</v>
-      </c>
-      <c r="K54" s="74"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="N54" s="77"/>
-      <c r="O54" s="78"/>
-      <c r="R54" s="10"/>
-    </row>
-    <row r="55" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="J55" s="75" t="s">
-        <v>17</v>
-      </c>
-      <c r="K55" s="75"/>
-      <c r="L55" s="75"/>
-      <c r="R55" s="10"/>
-    </row>
-    <row r="56" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H56" s="11"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="12"/>
-      <c r="N56" s="12"/>
-      <c r="O56" s="12"/>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
-      <c r="R56" s="13"/>
-    </row>
-    <row r="59" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="H59" s="43"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="55"/>
-    </row>
-    <row r="61" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="H61" s="43"/>
-      <c r="J61" s="55"/>
-      <c r="K61" s="55"/>
-    </row>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="M54:O54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="P50:R50"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="H46:R46"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="H24:L24"/>
-    <mergeCell ref="N24:R24"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="H35:L35"/>
-    <mergeCell ref="N35:R35"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="I2:R9"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:R13"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C14:C22">
-    <cfRule type="expression" dxfId="44" priority="39">
-      <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&lt;$E14)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="40">
+    <cfRule type="expression" dxfId="44" priority="40">
       <formula>AND(ISNUMBER($D14),ISNUMBER($E14),$D14&gt;$E14)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10228,42 +10439,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I22">
-    <cfRule type="expression" dxfId="28" priority="31">
+    <cfRule type="expression" dxfId="27" priority="31">
       <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="32">
+    <cfRule type="expression" dxfId="28" priority="32">
       <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:I33">
-    <cfRule type="expression" dxfId="26" priority="27">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="28">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36:I44">
-    <cfRule type="expression" dxfId="24" priority="23">
+    <cfRule type="expression" dxfId="23" priority="23">
       <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&lt;$K36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="24" priority="24">
       <formula>AND(ISNUMBER($J36),ISNUMBER($K36),$J36&gt;$K36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14:L22">
-    <cfRule type="expression" dxfId="22" priority="29">
+    <cfRule type="expression" dxfId="21" priority="29">
       <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&gt;$K14)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="30">
+    <cfRule type="expression" dxfId="22" priority="30">
       <formula>AND(ISNUMBER($J14),ISNUMBER($K14),$J14&lt;$K14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L25:L33">
-    <cfRule type="expression" dxfId="20" priority="25">
+    <cfRule type="expression" dxfId="19" priority="25">
       <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&gt;$K25)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="26">
+    <cfRule type="expression" dxfId="20" priority="26">
       <formula>AND(ISNUMBER($J25),ISNUMBER($K25),$J25&lt;$K25)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10276,65 +10487,65 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O14:O22">
-    <cfRule type="expression" dxfId="16" priority="11">
+    <cfRule type="expression" dxfId="15" priority="11">
       <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="16" priority="12">
       <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O25:O33">
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O36:O44">
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R14:R22">
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&gt;$Q14)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>AND(ISNUMBER($P14),ISNUMBER($Q14),$P14&lt;$Q14)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R25:R33">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&gt;$Q25)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND(ISNUMBER($P25),ISNUMBER($Q25),$P25&lt;$Q25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36:R44">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&gt;$Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(ISNUMBER($P36),ISNUMBER($Q36),$P36&lt;$Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I49:I52 L49:L54 O50:O51" xr:uid="{391306D2-D637-4EF1-86D7-BEE613482931}">
-      <formula1>"0,1,2,3"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C22 F14:F22 C25:C33 F25:F33 I14:I22 L14:L22 I25:I33 L25:L33 I36:I44 L36:L44 C36:C44 F36:F44 C47:C55 F47:F55 O14:O22 R14:R22 O25:O33 R25:R33 O36:O44 R36:R44" xr:uid="{97D60E3E-E640-4060-AEF6-3A299652B45F}">
+      <formula1>$B$3:$B$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O52:O53 R51:R52" xr:uid="{B1F90F2C-42E7-4F58-B62F-73321F1F12D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:E22 D25:E33 J14:K22 J25:K33 J36:K44 D36:E44 D47:E55 P14:Q22 P25:Q33 P36:Q44" xr:uid="{9416CC36-4C7B-4E76-AEAA-DB2C937A9A38}">
+      <formula1>"0,1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O52:O53 R51:R52" xr:uid="{53704A36-C010-4F3B-8824-03A9C2D76D97}">
       <formula1>"0,1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:E22 D25:E33 J14:K22 J25:K33 J36:K44 D36:E44 D47:E55 P14:Q22 P25:Q33 P36:Q44" xr:uid="{AE10AEFC-8CE0-4EC5-98E0-D887B5A6FE96}">
-      <formula1>"0,1,2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C22 F14:F22 C25:C33 F25:F33 I14:I22 L14:L22 I25:I33 L25:L33 I36:I44 L36:L44 C36:C44 F36:F44 C47:C55 F47:F55 O14:O22 R14:R22 O25:O33 R25:R33 O36:O44 R36:R44" xr:uid="{8B5F76B3-EC31-445D-9BA9-06D74D3FF936}">
-      <formula1>$B$3:$B$11</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I49:I52 L49:L54 O50:O51" xr:uid="{30D1ACD4-77FE-4960-97EB-CA60FFA175C1}">
+      <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
